--- a/tests/perf_v2/perf_history/v2.5/semantic_segmentation/SEMANTIC_SEGMENTATION-aggregated.xlsx
+++ b/tests/perf_v2/perf_history/v2.5/semantic_segmentation/SEMANTIC_SEGMENTATION-aggregated.xlsx
@@ -588,74 +588,74 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>150.3377</v>
+        <v>249.8699</v>
       </c>
       <c r="C2" t="n">
-        <v>41.6596</v>
+        <v>88.886</v>
       </c>
       <c r="D2" t="n">
-        <v>17</v>
+        <v>28.8</v>
       </c>
       <c r="E2" t="n">
-        <v>5.1478</v>
+        <v>10.7564</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0438</v>
+        <v>0.0442</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0002</v>
+        <v>0.0003</v>
       </c>
       <c r="H2" t="n">
-        <v>1.778</v>
+        <v>2.154</v>
       </c>
       <c r="I2" t="n">
-        <v>0.165</v>
+        <v>0.4724</v>
       </c>
       <c r="J2" t="n">
-        <v>0.7893</v>
+        <v>0.7922</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0027</v>
+        <v>0.0023</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7889</v>
+        <v>0.7917999999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0029</v>
+        <v>0.0021</v>
       </c>
       <c r="N2" t="n">
-        <v>0.7883</v>
+        <v>0.7911</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0028</v>
+        <v>0.0024</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0089</v>
+        <v>0.0092</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0002</v>
+        <v>0.0005</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0847</v>
+        <v>0.0861</v>
       </c>
       <c r="S2" t="n">
         <v>0.0009</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0555</v>
+        <v>0.0567</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0005</v>
+        <v>0.0009</v>
       </c>
       <c r="V2" t="n">
-        <v>15.4838</v>
+        <v>15.8301</v>
       </c>
       <c r="W2" t="n">
-        <v>0.1458</v>
+        <v>0.2404</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -670,12 +670,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -691,74 +691,74 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>309.3106</v>
+        <v>1449.2066</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9356</v>
+        <v>143.8108</v>
       </c>
       <c r="D3" t="n">
-        <v>12</v>
+        <v>58</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>5.7879</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1495</v>
+        <v>0.1563</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001</v>
+        <v>0.0004</v>
       </c>
       <c r="H3" t="n">
-        <v>2.748</v>
+        <v>2.834</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0286</v>
+        <v>0.0391</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7357</v>
+        <v>0.7919</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0046</v>
+        <v>0.0029</v>
       </c>
       <c r="L3" t="n">
-        <v>0.734</v>
+        <v>0.7892</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0044</v>
+        <v>0.0031</v>
       </c>
       <c r="N3" t="n">
-        <v>0.7313</v>
+        <v>0.7842</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0052</v>
+        <v>0.0027</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0137</v>
+        <v>0.0141</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.0008</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0483</v>
+        <v>0.0499</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0008</v>
+        <v>0.0011</v>
       </c>
       <c r="T3" t="n">
-        <v>0.059</v>
+        <v>0.0598</v>
       </c>
       <c r="U3" t="n">
         <v>0.0005999999999999999</v>
       </c>
       <c r="V3" t="n">
-        <v>16.4545</v>
+        <v>16.6749</v>
       </c>
       <c r="W3" t="n">
-        <v>0.1604</v>
+        <v>0.1727</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -773,12 +773,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -794,74 +794,74 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>276.8243</v>
+        <v>1243.1934</v>
       </c>
       <c r="C4" t="n">
-        <v>18.4977</v>
+        <v>186.2928</v>
       </c>
       <c r="D4" t="n">
-        <v>12.4</v>
+        <v>57.6</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8944</v>
+        <v>8.848699999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1293</v>
+        <v>0.1342</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0005</v>
+        <v>0.0009</v>
       </c>
       <c r="H4" t="n">
-        <v>1.542</v>
+        <v>1.72</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0936</v>
+        <v>0.0187</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7171999999999999</v>
+        <v>0.7638</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0083</v>
+        <v>0.0064</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7148</v>
+        <v>0.7621</v>
       </c>
       <c r="M4" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.0063</v>
       </c>
       <c r="N4" t="n">
-        <v>0.6727</v>
+        <v>0.7155</v>
       </c>
       <c r="O4" t="n">
-        <v>0.026</v>
+        <v>0.0135</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0116</v>
+        <v>0.0121</v>
       </c>
       <c r="Q4" t="n">
         <v>0.0004</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0513</v>
+        <v>0.0529</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.0009</v>
       </c>
       <c r="T4" t="n">
-        <v>0.068</v>
+        <v>0.0703</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0008</v>
+        <v>0.0012</v>
       </c>
       <c r="V4" t="n">
-        <v>18.9694</v>
+        <v>19.6224</v>
       </c>
       <c r="W4" t="n">
-        <v>0.2192</v>
+        <v>0.3223</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -876,12 +876,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -897,74 +897,74 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>827.3822</v>
+        <v>2996.1506</v>
       </c>
       <c r="C5" t="n">
-        <v>246.6316</v>
+        <v>411.8072</v>
       </c>
       <c r="D5" t="n">
-        <v>15.6</v>
+        <v>58.8</v>
       </c>
       <c r="E5" t="n">
-        <v>4.98</v>
+        <v>8.167</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3298</v>
+        <v>0.332</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0017</v>
+        <v>0.0005</v>
       </c>
       <c r="H5" t="n">
-        <v>8.853999999999999</v>
+        <v>8.901999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0371</v>
+        <v>0.0396</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7512</v>
+        <v>0.7952</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0182</v>
+        <v>0.004</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7486</v>
+        <v>0.792</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0178</v>
+        <v>0.0039</v>
       </c>
       <c r="N5" t="n">
-        <v>0.4906</v>
+        <v>0.433</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1563</v>
+        <v>0.1814</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0208</v>
+        <v>0.0217</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0004</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="R5" t="n">
-        <v>0.1197</v>
+        <v>0.1216</v>
       </c>
       <c r="S5" t="n">
         <v>0.0009</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1286</v>
+        <v>0.1317</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0009</v>
+        <v>0.0011</v>
       </c>
       <c r="V5" t="n">
-        <v>35.8866</v>
+        <v>36.7305</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2466</v>
+        <v>0.3067</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -979,12 +979,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1000,74 +1000,74 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>417.8663</v>
+        <v>2361.209</v>
       </c>
       <c r="C6" t="n">
-        <v>1.4258</v>
+        <v>376.0096</v>
       </c>
       <c r="D6" t="n">
-        <v>12</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>11.8659</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2018</v>
+        <v>0.2005</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0002</v>
+        <v>0.0001</v>
       </c>
       <c r="H6" t="n">
-        <v>7.424</v>
+        <v>7.51</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0537</v>
+        <v>0.0505</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7857</v>
+        <v>0.8250999999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0032</v>
+        <v>0.004</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7838000000000001</v>
+        <v>0.8228</v>
       </c>
       <c r="M6" t="n">
-        <v>0.003</v>
+        <v>0.0036</v>
       </c>
       <c r="N6" t="n">
-        <v>0.7752</v>
+        <v>0.8197</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0032</v>
+        <v>0.0052</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0157</v>
+        <v>0.016</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.0005</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0915</v>
+        <v>0.09180000000000001</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0004</v>
+        <v>0.0013</v>
       </c>
       <c r="T6" t="n">
-        <v>0.07149999999999999</v>
+        <v>0.07240000000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0007</v>
+        <v>0.0005</v>
       </c>
       <c r="V6" t="n">
-        <v>19.9576</v>
+        <v>20.1952</v>
       </c>
       <c r="W6" t="n">
-        <v>0.2091</v>
+        <v>0.1523</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1082,12 +1082,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1103,74 +1103,74 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>264.5395</v>
+        <v>1248.1917</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6979</v>
+        <v>253.4658</v>
       </c>
       <c r="D7" t="n">
-        <v>12</v>
+        <v>60.6</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>12.341</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1259</v>
+        <v>0.1264</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0003</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>4.744</v>
+        <v>5.038</v>
       </c>
       <c r="I7" t="n">
-        <v>0.059</v>
+        <v>0.0653</v>
       </c>
       <c r="J7" t="n">
-        <v>0.765</v>
+        <v>0.8107</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0055</v>
+        <v>0.0039</v>
       </c>
       <c r="L7" t="n">
-        <v>0.763</v>
+        <v>0.8088</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0053</v>
+        <v>0.0042</v>
       </c>
       <c r="N7" t="n">
-        <v>0.7606000000000001</v>
+        <v>0.8064</v>
       </c>
       <c r="O7" t="n">
-        <v>0.006</v>
+        <v>0.0047</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0116</v>
+        <v>0.0112</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.0002</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0577</v>
+        <v>0.0587</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0002</v>
+        <v>0.0016</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0484</v>
+        <v>0.0506</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0011</v>
+        <v>0.0031</v>
       </c>
       <c r="V7" t="n">
-        <v>13.4952</v>
+        <v>14.1276</v>
       </c>
       <c r="W7" t="n">
-        <v>0.3025</v>
+        <v>0.8779</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1206,74 +1206,74 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>237.408</v>
+        <v>1429.2097</v>
       </c>
       <c r="C8" t="n">
-        <v>0.399</v>
+        <v>106.1124</v>
       </c>
       <c r="D8" t="n">
-        <v>12</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>5.7706</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1139</v>
+        <v>0.1143</v>
       </c>
       <c r="G8" t="n">
         <v>0.0002</v>
       </c>
       <c r="H8" t="n">
-        <v>3.558</v>
+        <v>3.806</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1532</v>
+        <v>0.0956</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7341</v>
+        <v>0.8002</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0066</v>
+        <v>0.0027</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7324000000000001</v>
+        <v>0.7984</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0064</v>
+        <v>0.0027</v>
       </c>
       <c r="N8" t="n">
-        <v>0.7298</v>
+        <v>0.7963</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0051</v>
+        <v>0.0035</v>
       </c>
       <c r="P8" t="n">
-        <v>0.0095</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.0002</v>
+        <v>0.0003</v>
       </c>
       <c r="R8" t="n">
-        <v>0.0449</v>
+        <v>0.0452</v>
       </c>
       <c r="S8" t="n">
-        <v>0.001</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0449</v>
+        <v>0.047</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0005</v>
+        <v>0.0009</v>
       </c>
       <c r="V8" t="n">
-        <v>12.5209</v>
+        <v>13.1105</v>
       </c>
       <c r="W8" t="n">
-        <v>0.1425</v>
+        <v>0.2492</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1470,74 +1470,74 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>21.0512</v>
+        <v>24.6398</v>
       </c>
       <c r="C2" t="n">
-        <v>2.2781</v>
+        <v>9.434900000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>10.6</v>
+        <v>12.4</v>
       </c>
       <c r="E2" t="n">
-        <v>1.3416</v>
+        <v>5.3666</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0547</v>
+        <v>0.0543</v>
       </c>
       <c r="G2" t="n">
         <v>0.0002</v>
       </c>
       <c r="H2" t="n">
-        <v>1.33</v>
+        <v>1.312</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0834</v>
+        <v>0.1381</v>
       </c>
       <c r="J2" t="n">
-        <v>0.5934</v>
+        <v>0.5758</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0144</v>
+        <v>0.0315</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5921</v>
+        <v>0.5741000000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0142</v>
+        <v>0.0313</v>
       </c>
       <c r="N2" t="n">
-        <v>0.5931999999999999</v>
+        <v>0.5756</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0155</v>
+        <v>0.0343</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0274</v>
+        <v>0.0281</v>
       </c>
       <c r="Q2" t="n">
         <v>0.0007</v>
       </c>
       <c r="R2" t="n">
-        <v>0.2334</v>
+        <v>0.2342</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0043</v>
+        <v>0.0022</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6261</v>
+        <v>0.2323</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5717</v>
+        <v>0.0036</v>
       </c>
       <c r="V2" t="n">
-        <v>31.3072</v>
+        <v>11.6158</v>
       </c>
       <c r="W2" t="n">
-        <v>28.5856</v>
+        <v>0.1776</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -1552,12 +1552,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1573,74 +1573,74 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>41.9865</v>
+        <v>114.1059</v>
       </c>
       <c r="C3" t="n">
-        <v>0.3539</v>
+        <v>12.1216</v>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>28.6</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>3.2863</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1555</v>
+        <v>0.161</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0028</v>
+        <v>0.0005</v>
       </c>
       <c r="H3" t="n">
-        <v>2.88</v>
+        <v>2.906</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0274</v>
+        <v>0.0207</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2901</v>
+        <v>0.4226</v>
       </c>
       <c r="K3" t="n">
-        <v>0.006</v>
+        <v>0.0169</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2903</v>
+        <v>0.4217</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0061</v>
+        <v>0.0172</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2891</v>
+        <v>0.4172</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0064</v>
+        <v>0.0182</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0361</v>
+        <v>0.0406</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0027</v>
+        <v>0.0034</v>
       </c>
       <c r="R3" t="n">
-        <v>0.2386</v>
+        <v>0.2456</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0166</v>
+        <v>0.0094</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5098</v>
+        <v>0.3028</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1415</v>
+        <v>0.0132</v>
       </c>
       <c r="V3" t="n">
-        <v>25.4888</v>
+        <v>15.1403</v>
       </c>
       <c r="W3" t="n">
-        <v>7.0741</v>
+        <v>0.6611</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1676,74 +1676,74 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>35.7424</v>
+        <v>105.5346</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2545</v>
+        <v>17.3115</v>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>5.1962</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1274</v>
+        <v>0.1345</v>
       </c>
       <c r="G4" t="n">
-        <v>0.002</v>
+        <v>0.0015</v>
       </c>
       <c r="H4" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0822</v>
+        <v>0.0951</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2776</v>
+        <v>0.3992</v>
       </c>
       <c r="K4" t="n">
-        <v>0.007</v>
+        <v>0.0219</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2778</v>
+        <v>0.3987</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0069</v>
+        <v>0.0218</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2537</v>
+        <v>0.3433</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0124</v>
+        <v>0.0441</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0311</v>
+        <v>0.0319</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.0009</v>
       </c>
       <c r="R4" t="n">
-        <v>0.39</v>
+        <v>0.4001</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0046</v>
+        <v>0.0029</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5978</v>
+        <v>0.4711</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0397</v>
+        <v>0.0067</v>
       </c>
       <c r="V4" t="n">
-        <v>29.8913</v>
+        <v>23.5566</v>
       </c>
       <c r="W4" t="n">
-        <v>1.9853</v>
+        <v>0.3367</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1758,12 +1758,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1779,74 +1779,74 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>80.5091</v>
+        <v>159.4236</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2004</v>
+        <v>62.7364</v>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>20.8</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>8.642899999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3274</v>
+        <v>0.3313</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0009</v>
+        <v>0.0017</v>
       </c>
       <c r="H5" t="n">
-        <v>8.842000000000001</v>
+        <v>8.914</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0045</v>
+        <v>0.0796</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2834</v>
+        <v>0.3572</v>
       </c>
       <c r="K5" t="n">
-        <v>0.012</v>
+        <v>0.0629</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2836</v>
+        <v>0.357</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0121</v>
+        <v>0.06270000000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>0.23</v>
+        <v>0.2548</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0104</v>
+        <v>0.0464</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0577</v>
+        <v>0.0562</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0008</v>
+        <v>0.0033</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3422</v>
+        <v>0.3426</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0207</v>
+        <v>0.0071</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5122</v>
+        <v>0.4856</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0073</v>
+        <v>0.0028</v>
       </c>
       <c r="V5" t="n">
-        <v>25.6087</v>
+        <v>24.2822</v>
       </c>
       <c r="W5" t="n">
-        <v>0.3636</v>
+        <v>0.1381</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1861,12 +1861,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1882,22 +1882,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>56.0502</v>
+        <v>139.2863</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1081</v>
+        <v>42.8366</v>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>26.8</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>8.642899999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2064</v>
+        <v>0.2053</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0008</v>
+        <v>0.0004</v>
       </c>
       <c r="H6" t="n">
         <v>7.672</v>
@@ -1906,50 +1906,50 @@
         <v>0.0939</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2669</v>
+        <v>0.4192</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0028</v>
+        <v>0.0781</v>
       </c>
       <c r="L6" t="n">
+        <v>0.4186</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.0781</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.3585</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.0505</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.0474</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.0031</v>
+      </c>
+      <c r="R6" t="n">
         <v>0.2666</v>
       </c>
-      <c r="M6" t="n">
-        <v>0.0027</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0.2619</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0.0052</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0.0447</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0.0008</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0.2648</v>
-      </c>
       <c r="S6" t="n">
-        <v>0.0204</v>
+        <v>0.0123</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4509</v>
+        <v>0.2988</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1998</v>
+        <v>0.0045</v>
       </c>
       <c r="V6" t="n">
-        <v>22.5439</v>
+        <v>14.9412</v>
       </c>
       <c r="W6" t="n">
-        <v>9.989800000000001</v>
+        <v>0.2246</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1964,12 +1964,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1985,74 +1985,74 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>36.226</v>
+        <v>120.2489</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1109</v>
+        <v>47.1057</v>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>36.4</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>14.758</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1233</v>
+        <v>0.1239</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0004</v>
+        <v>0.0002</v>
       </c>
       <c r="H7" t="n">
-        <v>4.568</v>
+        <v>4.62</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0249</v>
+        <v>0.1037</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2589</v>
+        <v>0.3826</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0014</v>
+        <v>0.09909999999999999</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2588</v>
+        <v>0.3821</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0011</v>
+        <v>0.09909999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>0.258</v>
+        <v>0.3798</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0017</v>
+        <v>0.0992</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0354</v>
+        <v>0.0314</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0035</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2234</v>
+        <v>0.2246</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0142</v>
+        <v>0.0072</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5667</v>
+        <v>0.2394</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5026</v>
+        <v>0.0064</v>
       </c>
       <c r="V7" t="n">
-        <v>28.3341</v>
+        <v>11.9687</v>
       </c>
       <c r="W7" t="n">
-        <v>25.1312</v>
+        <v>0.3201</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -2067,12 +2067,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -2088,74 +2088,74 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>32.0952</v>
+        <v>161.4605</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1612</v>
+        <v>44.8127</v>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>55.6</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>16.0717</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1105</v>
+        <v>0.1126</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0007</v>
+        <v>0.0009</v>
       </c>
       <c r="H8" t="n">
-        <v>3.39</v>
+        <v>3.464</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>0.0241</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2449</v>
+        <v>0.3997</v>
       </c>
       <c r="K8" t="n">
-        <v>0.005</v>
+        <v>0.0641</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2449</v>
+        <v>0.3995</v>
       </c>
       <c r="M8" t="n">
-        <v>0.005</v>
+        <v>0.0641</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2418</v>
+        <v>0.3828</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0056</v>
+        <v>0.0536</v>
       </c>
       <c r="P8" t="n">
-        <v>0.0291</v>
+        <v>0.0283</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.003</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="R8" t="n">
-        <v>0.2122</v>
+        <v>0.2192</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0039</v>
+        <v>0.0022</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4078</v>
+        <v>0.2494</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3603</v>
+        <v>0.0044</v>
       </c>
       <c r="V8" t="n">
-        <v>20.3876</v>
+        <v>12.4684</v>
       </c>
       <c r="W8" t="n">
-        <v>18.0137</v>
+        <v>0.2214</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -2352,74 +2352,74 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>114.7565</v>
+        <v>177.0713</v>
       </c>
       <c r="C2" t="n">
-        <v>3.573</v>
+        <v>40.2343</v>
       </c>
       <c r="D2" t="n">
-        <v>13.2</v>
+        <v>20.8</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4472</v>
+        <v>4.9699</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0572</v>
+        <v>0.0576</v>
       </c>
       <c r="G2" t="n">
         <v>0.0002</v>
       </c>
       <c r="H2" t="n">
-        <v>3.004</v>
+        <v>3.062</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2875</v>
+        <v>0.2199</v>
       </c>
       <c r="J2" t="n">
-        <v>0.8589</v>
+        <v>0.8665</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0026</v>
+        <v>0.0045</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8573</v>
+        <v>0.8649</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0024</v>
+        <v>0.0048</v>
       </c>
       <c r="N2" t="n">
-        <v>0.8568</v>
+        <v>0.8645</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0025</v>
+        <v>0.0056</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0095</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0002</v>
+        <v>0.0001</v>
       </c>
       <c r="R2" t="n">
-        <v>0.1125</v>
+        <v>0.1163</v>
       </c>
       <c r="S2" t="n">
+        <v>0.0014</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.0919</v>
+      </c>
+      <c r="U2" t="n">
         <v>0.0017</v>
       </c>
-      <c r="T2" t="n">
-        <v>0.09370000000000001</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0.0053</v>
-      </c>
       <c r="V2" t="n">
-        <v>28.1196</v>
+        <v>27.5844</v>
       </c>
       <c r="W2" t="n">
-        <v>1.5762</v>
+        <v>0.4961</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -2434,12 +2434,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -2455,74 +2455,74 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>230.608</v>
+        <v>1119.2089</v>
       </c>
       <c r="C3" t="n">
-        <v>7.5844</v>
+        <v>242.9613</v>
       </c>
       <c r="D3" t="n">
-        <v>12.2</v>
+        <v>62.6</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4472</v>
+        <v>14.0641</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1548</v>
+        <v>0.1597</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0007</v>
+        <v>0.0014</v>
       </c>
       <c r="H3" t="n">
-        <v>3.336</v>
+        <v>3.562</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0888</v>
+        <v>0.1047</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2328</v>
+        <v>0.4549</v>
       </c>
       <c r="K3" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.021</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2321</v>
+        <v>0.4519</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0086</v>
+        <v>0.0216</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2233</v>
+        <v>0.4236</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0065</v>
+        <v>0.0192</v>
       </c>
       <c r="P3" t="n">
-        <v>0.014</v>
+        <v>0.0143</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.0005</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0882</v>
+        <v>0.0912</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0018</v>
+        <v>0.0016</v>
       </c>
       <c r="T3" t="n">
-        <v>0.09420000000000001</v>
+        <v>0.099</v>
       </c>
       <c r="U3" t="n">
-        <v>0.001</v>
+        <v>0.0016</v>
       </c>
       <c r="V3" t="n">
-        <v>28.2652</v>
+        <v>29.6972</v>
       </c>
       <c r="W3" t="n">
-        <v>0.2969</v>
+        <v>0.4701</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -2558,74 +2558,74 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>213.2678</v>
+        <v>1062.0106</v>
       </c>
       <c r="C4" t="n">
-        <v>11.3029</v>
+        <v>228.0649</v>
       </c>
       <c r="D4" t="n">
-        <v>13</v>
+        <v>68.2</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7071</v>
+        <v>14.9566</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1342</v>
+        <v>0.1374</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0008</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>2.222</v>
+        <v>2.43</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1303</v>
+        <v>0.1068</v>
       </c>
       <c r="J4" t="n">
-        <v>0.22</v>
+        <v>0.421</v>
       </c>
       <c r="K4" t="n">
-        <v>0.012</v>
+        <v>0.0461</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2191</v>
+        <v>0.4206</v>
       </c>
       <c r="M4" t="n">
-        <v>0.012</v>
+        <v>0.0462</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1467</v>
+        <v>0.1566</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0271</v>
+        <v>0.0689</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0121</v>
+        <v>0.0128</v>
       </c>
       <c r="Q4" t="n">
         <v>0.0005</v>
       </c>
       <c r="R4" t="n">
-        <v>0.1482</v>
+        <v>0.1501</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0018</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1607</v>
+        <v>0.1654</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0024</v>
+        <v>0.0045</v>
       </c>
       <c r="V4" t="n">
-        <v>48.2229</v>
+        <v>49.6088</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7244</v>
+        <v>1.3431</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -2640,12 +2640,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2661,74 +2661,74 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>465.0298</v>
+        <v>2320.8871</v>
       </c>
       <c r="C5" t="n">
-        <v>28.149</v>
+        <v>269.3897</v>
       </c>
       <c r="D5" t="n">
-        <v>12.8</v>
+        <v>67.8</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8367</v>
+        <v>8.012499999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3304</v>
+        <v>0.3339</v>
       </c>
       <c r="G5" t="n">
         <v>0.0004</v>
       </c>
       <c r="H5" t="n">
-        <v>9.398</v>
+        <v>9.458</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0507</v>
+        <v>0.0239</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1628</v>
+        <v>0.3777</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0184</v>
+        <v>0.0205</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1619</v>
+        <v>0.3778</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0183</v>
+        <v>0.0212</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0716</v>
+        <v>0.0762</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0143</v>
+        <v>0.0238</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0216</v>
+        <v>0.0221</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0001</v>
+        <v>0.0003</v>
       </c>
       <c r="R5" t="n">
-        <v>0.152</v>
+        <v>0.1571</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0007</v>
+        <v>0.0017</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1624</v>
+        <v>0.168</v>
       </c>
       <c r="U5" t="n">
         <v>0.0014</v>
       </c>
       <c r="V5" t="n">
-        <v>48.7052</v>
+        <v>50.3969</v>
       </c>
       <c r="W5" t="n">
-        <v>0.4315</v>
+        <v>0.4226</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -2743,12 +2743,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2764,74 +2764,74 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>295.8738</v>
+        <v>664.6531</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7325</v>
+        <v>133.4001</v>
       </c>
       <c r="D6" t="n">
-        <v>12</v>
+        <v>28.8</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>6.0992</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2062</v>
+        <v>0.2049</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0007</v>
+        <v>0.0002</v>
       </c>
       <c r="H6" t="n">
-        <v>8.282</v>
+        <v>8.316000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0687</v>
+        <v>0.07920000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8111</v>
+        <v>0.8297</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0086</v>
+        <v>0.0073</v>
       </c>
       <c r="L6" t="n">
-        <v>0.8086</v>
+        <v>0.8274</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0086</v>
+        <v>0.0068</v>
       </c>
       <c r="N6" t="n">
-        <v>0.7998</v>
+        <v>0.8192</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0069</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0161</v>
+        <v>0.0162</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0001</v>
+        <v>0.0004</v>
       </c>
       <c r="R6" t="n">
-        <v>0.1247</v>
+        <v>0.1261</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0039</v>
+        <v>0.001</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1161</v>
+        <v>0.1103</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0094</v>
+        <v>0.0023</v>
       </c>
       <c r="V6" t="n">
-        <v>34.8268</v>
+        <v>33.0923</v>
       </c>
       <c r="W6" t="n">
-        <v>2.8175</v>
+        <v>0.6991000000000001</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -2867,74 +2867,74 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>195.3845</v>
+        <v>681.3765</v>
       </c>
       <c r="C7" t="n">
-        <v>0.613</v>
+        <v>96.3352</v>
       </c>
       <c r="D7" t="n">
-        <v>12</v>
+        <v>45.4</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>6.6933</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1302</v>
+        <v>0.1293</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0003</v>
+        <v>0.0011</v>
       </c>
       <c r="H7" t="n">
-        <v>5.764</v>
+        <v>6.048</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2094</v>
+        <v>0.1966</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7223000000000001</v>
+        <v>0.8053</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0291</v>
+        <v>0.0048</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7194</v>
+        <v>0.803</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03</v>
+        <v>0.0055</v>
       </c>
       <c r="N7" t="n">
-        <v>0.7151999999999999</v>
+        <v>0.7992</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0342</v>
+        <v>0.0042</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0116</v>
+        <v>0.0118</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0001</v>
+        <v>0.0002</v>
       </c>
       <c r="R7" t="n">
-        <v>0.09379999999999999</v>
+        <v>0.0954</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0007</v>
+        <v>0.0008</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0861</v>
+        <v>0.0868</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0016</v>
+        <v>0.0031</v>
       </c>
       <c r="V7" t="n">
-        <v>25.8264</v>
+        <v>26.0271</v>
       </c>
       <c r="W7" t="n">
-        <v>0.484</v>
+        <v>0.9367</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -2949,12 +2949,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -2970,74 +2970,74 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>175.2208</v>
+        <v>745.4105</v>
       </c>
       <c r="C8" t="n">
-        <v>1.4894</v>
+        <v>121.3614</v>
       </c>
       <c r="D8" t="n">
-        <v>12</v>
+        <v>55</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>9.055400000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1175</v>
+        <v>0.1185</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0011</v>
+        <v>0.0018</v>
       </c>
       <c r="H8" t="n">
-        <v>4.134</v>
+        <v>4.562</v>
       </c>
       <c r="I8" t="n">
-        <v>0.123</v>
+        <v>0.0526</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5532</v>
+        <v>0.7783</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0369</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5515</v>
+        <v>0.7763</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0374</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>0.4787</v>
+        <v>0.7734</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1514</v>
+        <v>0.01</v>
       </c>
       <c r="P8" t="n">
-        <v>0.0106</v>
+        <v>0.0105</v>
       </c>
       <c r="Q8" t="n">
+        <v>0.0007</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.0861</v>
+      </c>
+      <c r="S8" t="n">
         <v>0.0005999999999999999</v>
       </c>
-      <c r="R8" t="n">
-        <v>0.08210000000000001</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0.0012</v>
-      </c>
       <c r="T8" t="n">
-        <v>0.0824</v>
+        <v>0.0873</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0024</v>
+        <v>0.0021</v>
       </c>
       <c r="V8" t="n">
-        <v>24.7238</v>
+        <v>26.1769</v>
       </c>
       <c r="W8" t="n">
-        <v>0.7149</v>
+        <v>0.6311</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -3234,74 +3234,74 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>20.066</v>
+        <v>24.4761</v>
       </c>
       <c r="C2" t="n">
-        <v>1.5728</v>
+        <v>6.4351</v>
       </c>
       <c r="D2" t="n">
-        <v>20.4</v>
+        <v>24.4</v>
       </c>
       <c r="E2" t="n">
-        <v>2.0736</v>
+        <v>6.9498</v>
       </c>
       <c r="F2" t="n">
-        <v>0.056</v>
+        <v>0.0561</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0002</v>
+        <v>0.0005</v>
       </c>
       <c r="H2" t="n">
-        <v>1.162</v>
+        <v>1.202</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0045</v>
+        <v>0.08840000000000001</v>
       </c>
       <c r="J2" t="n">
-        <v>0.5295</v>
+        <v>0.5357</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0089</v>
+        <v>0.0106</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5296</v>
+        <v>0.5357</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0091</v>
+        <v>0.0107</v>
       </c>
       <c r="N2" t="n">
-        <v>0.5283</v>
+        <v>0.5346</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0097</v>
+        <v>0.0106</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0382</v>
+        <v>0.0406</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="R2" t="n">
-        <v>0.2832</v>
+        <v>0.2932</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0101</v>
+        <v>0.0042</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2968</v>
+        <v>0.3101</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0212</v>
+        <v>0.0074</v>
       </c>
       <c r="V2" t="n">
-        <v>8.9055</v>
+        <v>9.3024</v>
       </c>
       <c r="W2" t="n">
-        <v>0.6353</v>
+        <v>0.2216</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -3337,74 +3337,74 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>32.7298</v>
+        <v>74.7328</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5842000000000001</v>
+        <v>31.104</v>
       </c>
       <c r="D3" t="n">
-        <v>19.4</v>
+        <v>44.8</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5477</v>
+        <v>19.6774</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1402</v>
+        <v>0.1517</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0011</v>
+        <v>0.0009</v>
       </c>
       <c r="H3" t="n">
-        <v>3.01</v>
+        <v>3.06</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0.201</v>
+        <v>0.2986</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0109</v>
+        <v>0.0982</v>
       </c>
       <c r="L3" t="n">
-        <v>0.201</v>
+        <v>0.2982</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0108</v>
+        <v>0.0975</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2003</v>
+        <v>0.2923</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0112</v>
+        <v>0.0956</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0529</v>
+        <v>0.0569</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0015</v>
+        <v>0.0042</v>
       </c>
       <c r="R3" t="n">
-        <v>0.3116</v>
+        <v>0.3122</v>
       </c>
       <c r="S3" t="n">
-        <v>0.035</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4366</v>
+        <v>0.3927</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0572</v>
+        <v>0.0153</v>
       </c>
       <c r="V3" t="n">
-        <v>13.0975</v>
+        <v>11.7802</v>
       </c>
       <c r="W3" t="n">
-        <v>1.7168</v>
+        <v>0.4582</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -3419,12 +3419,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -3440,74 +3440,74 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>27.9438</v>
+        <v>54.3158</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2937</v>
+        <v>5.9872</v>
       </c>
       <c r="D4" t="n">
-        <v>19</v>
+        <v>37.6</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>4.5607</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1159</v>
+        <v>0.1239</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0028</v>
+        <v>0.0019</v>
       </c>
       <c r="H4" t="n">
-        <v>1.44</v>
+        <v>1.442</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>0.0045</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1775</v>
+        <v>0.2439</v>
       </c>
       <c r="K4" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.0194</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1773</v>
+        <v>0.2439</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0077</v>
+        <v>0.0194</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1472</v>
+        <v>0.1789</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0141</v>
+        <v>0.0464</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0452</v>
+        <v>0.0489</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.001</v>
+        <v>0.0016</v>
       </c>
       <c r="R4" t="n">
-        <v>0.4252</v>
+        <v>0.4523</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0038</v>
+        <v>0.0078</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5473</v>
+        <v>0.5653</v>
       </c>
       <c r="U4" t="n">
-        <v>0.029</v>
+        <v>0.0199</v>
       </c>
       <c r="V4" t="n">
-        <v>16.4196</v>
+        <v>16.9577</v>
       </c>
       <c r="W4" t="n">
-        <v>0.871</v>
+        <v>0.5984</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -3522,12 +3522,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -3543,74 +3543,74 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>59.9456</v>
+        <v>136.0986</v>
       </c>
       <c r="C5" t="n">
-        <v>0.148</v>
+        <v>42.4121</v>
       </c>
       <c r="D5" t="n">
-        <v>19</v>
+        <v>44.8</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>14.5327</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3259</v>
+        <v>0.332</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0023</v>
+        <v>0.0031</v>
       </c>
       <c r="H5" t="n">
-        <v>8.91</v>
+        <v>8.917999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>0.0179</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1788</v>
+        <v>0.2639</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0105</v>
+        <v>0.0595</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1786</v>
+        <v>0.2635</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0106</v>
+        <v>0.0593</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1195</v>
+        <v>0.1142</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0171</v>
+        <v>0.0387</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0785</v>
+        <v>0.09089999999999999</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0004</v>
+        <v>0.0013</v>
       </c>
       <c r="R5" t="n">
-        <v>0.433</v>
+        <v>0.4374</v>
       </c>
       <c r="S5" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.0113</v>
       </c>
       <c r="T5" t="n">
-        <v>0.7232</v>
+        <v>0.7069</v>
       </c>
       <c r="U5" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.0271</v>
       </c>
       <c r="V5" t="n">
-        <v>21.6955</v>
+        <v>21.2056</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2886</v>
+        <v>0.8121</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -3646,74 +3646,74 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>45.1867</v>
+        <v>135.6359</v>
       </c>
       <c r="C6" t="n">
-        <v>0.241</v>
+        <v>35.2028</v>
       </c>
       <c r="D6" t="n">
-        <v>19</v>
+        <v>62.4</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>16.6373</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1997</v>
+        <v>0.1987</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0015</v>
+        <v>0.0003</v>
       </c>
       <c r="H6" t="n">
-        <v>7.77</v>
+        <v>7.772</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>0.0045</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1169</v>
+        <v>0.3039</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0067</v>
+        <v>0.09329999999999999</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1169</v>
+        <v>0.3037</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0067</v>
+        <v>0.0931</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1134</v>
+        <v>0.2856</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0098</v>
+        <v>0.099</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0689</v>
+        <v>0.0693</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0049</v>
+        <v>0.0053</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3183</v>
+        <v>0.3488</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0114</v>
+        <v>0.0078</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4573</v>
+        <v>0.406</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0491</v>
+        <v>0.0141</v>
       </c>
       <c r="V6" t="n">
-        <v>13.7194</v>
+        <v>12.1801</v>
       </c>
       <c r="W6" t="n">
-        <v>1.4724</v>
+        <v>0.4224</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -3728,12 +3728,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3749,22 +3749,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>29.6677</v>
+        <v>64.33280000000001</v>
       </c>
       <c r="C7" t="n">
-        <v>0.134</v>
+        <v>17.2109</v>
       </c>
       <c r="D7" t="n">
-        <v>19</v>
+        <v>43.2</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>12.4579</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1191</v>
+        <v>0.1194</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0007</v>
+        <v>0.0004</v>
       </c>
       <c r="H7" t="n">
         <v>4.664</v>
@@ -3773,50 +3773,50 @@
         <v>0.0055</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1146</v>
+        <v>0.1567</v>
       </c>
       <c r="K7" t="n">
+        <v>0.0257</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.1567</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.0258</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.1571</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.0254</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.0505</v>
+      </c>
+      <c r="Q7" t="n">
         <v>0.0051</v>
       </c>
-      <c r="L7" t="n">
-        <v>0.1146</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0.1128</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0.0046</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0.0497</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0.0043</v>
-      </c>
       <c r="R7" t="n">
-        <v>0.305</v>
+        <v>0.2765</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0039</v>
+        <v>0.01</v>
       </c>
       <c r="T7" t="n">
-        <v>0.7131</v>
+        <v>0.3159</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1943</v>
+        <v>0.012</v>
       </c>
       <c r="V7" t="n">
-        <v>21.3925</v>
+        <v>9.478199999999999</v>
       </c>
       <c r="W7" t="n">
-        <v>5.8276</v>
+        <v>0.3588</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -3831,12 +3831,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3852,22 +3852,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>25.7505</v>
+        <v>48.8456</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1223</v>
+        <v>26.0556</v>
       </c>
       <c r="D8" t="n">
-        <v>19</v>
+        <v>37.6</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>21.2791</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1033</v>
+        <v>0.1049</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0009</v>
+        <v>0.001</v>
       </c>
       <c r="H8" t="n">
         <v>3.51</v>
@@ -3876,50 +3876,50 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0941</v>
+        <v>0.111</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0226</v>
+        <v>0.0406</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0941</v>
+        <v>0.111</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0225</v>
+        <v>0.0407</v>
       </c>
       <c r="N8" t="n">
-        <v>0.08069999999999999</v>
+        <v>0.1109</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0381</v>
+        <v>0.0406</v>
       </c>
       <c r="P8" t="n">
-        <v>0.0474</v>
+        <v>0.0452</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.0056</v>
+        <v>0.0045</v>
       </c>
       <c r="R8" t="n">
-        <v>0.2674</v>
+        <v>0.2785</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0036</v>
+        <v>0.0109</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3218</v>
+        <v>0.3306</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0113</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="V8" t="n">
-        <v>9.6541</v>
+        <v>9.918200000000001</v>
       </c>
       <c r="W8" t="n">
-        <v>0.3384</v>
+        <v>0.287</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -3934,12 +3934,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -4116,22 +4116,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>45.3187</v>
+        <v>47.3548</v>
       </c>
       <c r="C2" t="n">
-        <v>1.1324</v>
+        <v>3.3678</v>
       </c>
       <c r="D2" t="n">
-        <v>38.4</v>
+        <v>39.2</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5477</v>
+        <v>2.6833</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0374</v>
+        <v>0.035</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0021</v>
+        <v>0.0035</v>
       </c>
       <c r="H2" t="n">
         <v>0.68</v>
@@ -4140,50 +4140,50 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0.8305</v>
+        <v>0.8331</v>
       </c>
       <c r="K2" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.0113</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8308</v>
+        <v>0.8338</v>
       </c>
       <c r="M2" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.0112</v>
       </c>
       <c r="N2" t="n">
-        <v>0.8277</v>
+        <v>0.8313</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0067</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="P2" t="n">
-        <v>0.137</v>
+        <v>0.1406</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0021</v>
+        <v>0.0017</v>
       </c>
       <c r="R2" t="n">
-        <v>0.6847</v>
+        <v>0.697</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0271</v>
+        <v>0.0101</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7217</v>
+        <v>0.7272</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0474</v>
+        <v>0.0126</v>
       </c>
       <c r="V2" t="n">
-        <v>8.660500000000001</v>
+        <v>8.726699999999999</v>
       </c>
       <c r="W2" t="n">
-        <v>0.5689</v>
+        <v>0.1517</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -4219,22 +4219,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>60.299</v>
+        <v>64.2683</v>
       </c>
       <c r="C3" t="n">
-        <v>1.7324</v>
+        <v>3.916</v>
       </c>
       <c r="D3" t="n">
-        <v>38.6</v>
+        <v>39.8</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5477</v>
+        <v>2.3875</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1461</v>
+        <v>0.1521</v>
       </c>
       <c r="G3" t="n">
-        <v>0.004</v>
+        <v>0.0023</v>
       </c>
       <c r="H3" t="n">
         <v>2.32</v>
@@ -4243,50 +4243,50 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8157</v>
+        <v>0.8316</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0246</v>
+        <v>0.016</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8158</v>
+        <v>0.8324</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0245</v>
+        <v>0.0151</v>
       </c>
       <c r="N3" t="n">
-        <v>0.8192</v>
+        <v>0.8371</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0252</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1615</v>
+        <v>0.1691</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0126</v>
+        <v>0.0122</v>
       </c>
       <c r="R3" t="n">
-        <v>0.7323</v>
+        <v>0.7759</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0221</v>
+        <v>0.0306</v>
       </c>
       <c r="T3" t="n">
-        <v>1.083</v>
+        <v>0.9292</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1918</v>
+        <v>0.0209</v>
       </c>
       <c r="V3" t="n">
-        <v>12.996</v>
+        <v>11.1501</v>
       </c>
       <c r="W3" t="n">
-        <v>2.3021</v>
+        <v>0.2507</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -4301,12 +4301,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -4322,22 +4322,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>55.0502</v>
+        <v>61.3298</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6252</v>
+        <v>6.2247</v>
       </c>
       <c r="D4" t="n">
-        <v>38.2</v>
+        <v>41</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4472</v>
+        <v>4.4721</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1178</v>
+        <v>0.1255</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0018</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="H4" t="n">
         <v>1.07</v>
@@ -4346,50 +4346,50 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7973</v>
+        <v>0.8065</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0184</v>
+        <v>0.0205</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7962</v>
+        <v>0.8062</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0182</v>
+        <v>0.0205</v>
       </c>
       <c r="N4" t="n">
-        <v>0.6898</v>
+        <v>0.745</v>
       </c>
       <c r="O4" t="n">
-        <v>0.018</v>
+        <v>0.0563</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1448</v>
+        <v>0.1582</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0033</v>
+        <v>0.0109</v>
       </c>
       <c r="R4" t="n">
-        <v>1.2296</v>
+        <v>1.2438</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0584</v>
+        <v>0.0477</v>
       </c>
       <c r="T4" t="n">
-        <v>1.389</v>
+        <v>1.4486</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0411</v>
+        <v>0.0383</v>
       </c>
       <c r="V4" t="n">
-        <v>16.668</v>
+        <v>17.383</v>
       </c>
       <c r="W4" t="n">
-        <v>0.4933</v>
+        <v>0.4597</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -4404,12 +4404,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -4425,22 +4425,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>79.9649</v>
+        <v>92.7122</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7137</v>
+        <v>10.8141</v>
       </c>
       <c r="D5" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>5.4772</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3081</v>
+        <v>0.3156</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0035</v>
+        <v>0.0022</v>
       </c>
       <c r="H5" t="n">
         <v>8.539999999999999</v>
@@ -4449,50 +4449,50 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8249</v>
+        <v>0.8608</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0141</v>
+        <v>0.013</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8254</v>
+        <v>0.8599</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0144</v>
+        <v>0.0133</v>
       </c>
       <c r="N5" t="n">
-        <v>0.6812</v>
+        <v>0.6912</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0315</v>
+        <v>0.0277</v>
       </c>
       <c r="P5" t="n">
-        <v>0.228</v>
+        <v>0.2452</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0136</v>
+        <v>0.0041</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9626</v>
+        <v>0.9916</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0201</v>
+        <v>0.0191</v>
       </c>
       <c r="T5" t="n">
-        <v>1.5178</v>
+        <v>1.5693</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0232</v>
+        <v>0.012</v>
       </c>
       <c r="V5" t="n">
-        <v>18.2138</v>
+        <v>18.8311</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2782</v>
+        <v>0.144</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -4507,12 +4507,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -4528,22 +4528,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>69.44629999999999</v>
+        <v>84.7109</v>
       </c>
       <c r="C6" t="n">
-        <v>0.4854</v>
+        <v>24.5372</v>
       </c>
       <c r="D6" t="n">
-        <v>38.2</v>
+        <v>46.4</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4472</v>
+        <v>13.5019</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1823</v>
+        <v>0.1829</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0016</v>
+        <v>0.0003</v>
       </c>
       <c r="H6" t="n">
         <v>7.13</v>
@@ -4552,50 +4552,50 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6897</v>
+        <v>0.6923</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0423</v>
+        <v>0.0746</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6902</v>
+        <v>0.6912</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0416</v>
+        <v>0.07489999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>0.6098</v>
+        <v>0.5981</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0649</v>
+        <v>0.0983</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2144</v>
+        <v>0.205</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0016</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="R6" t="n">
-        <v>0.7531</v>
+        <v>0.7593</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0147</v>
+        <v>0.0124</v>
       </c>
       <c r="T6" t="n">
-        <v>0.9407</v>
+        <v>0.9469</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0261</v>
+        <v>0.0145</v>
       </c>
       <c r="V6" t="n">
-        <v>11.2888</v>
+        <v>11.3627</v>
       </c>
       <c r="W6" t="n">
-        <v>0.313</v>
+        <v>0.1737</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -4610,12 +4610,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -4631,74 +4631,74 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>54.5983</v>
+        <v>58.9315</v>
       </c>
       <c r="C7" t="n">
-        <v>0.4006</v>
+        <v>1.7498</v>
       </c>
       <c r="D7" t="n">
-        <v>38</v>
+        <v>38.8</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>0.4472</v>
       </c>
       <c r="F7" t="n">
-        <v>0.11</v>
+        <v>0.1114</v>
       </c>
       <c r="G7" t="n">
         <v>0.0005</v>
       </c>
       <c r="H7" t="n">
-        <v>4.21</v>
+        <v>4.216</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>0.0055</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7131</v>
+        <v>0.7195</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0324</v>
+        <v>0.027</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7126</v>
+        <v>0.7181999999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0316</v>
+        <v>0.0272</v>
       </c>
       <c r="N7" t="n">
-        <v>0.7191</v>
+        <v>0.7062</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0226</v>
+        <v>0.029</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1617</v>
+        <v>0.1779</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0144</v>
+        <v>0.0062</v>
       </c>
       <c r="R7" t="n">
-        <v>0.6243</v>
+        <v>0.6599</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0048</v>
+        <v>0.0115</v>
       </c>
       <c r="T7" t="n">
-        <v>0.9792</v>
+        <v>0.7392</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3472</v>
+        <v>0.0145</v>
       </c>
       <c r="V7" t="n">
-        <v>11.7504</v>
+        <v>8.8706</v>
       </c>
       <c r="W7" t="n">
-        <v>4.1667</v>
+        <v>0.1743</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -4713,12 +4713,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -4734,22 +4734,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>51.9625</v>
+        <v>55.3798</v>
       </c>
       <c r="C8" t="n">
-        <v>1.1694</v>
+        <v>1.123</v>
       </c>
       <c r="D8" t="n">
-        <v>38.2</v>
+        <v>38.8</v>
       </c>
       <c r="E8" t="n">
         <v>0.4472</v>
       </c>
       <c r="F8" t="n">
-        <v>0.09909999999999999</v>
+        <v>0.1015</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0007</v>
+        <v>0.001</v>
       </c>
       <c r="H8" t="n">
         <v>2.81</v>
@@ -4758,50 +4758,50 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6832</v>
+        <v>0.7058</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0368</v>
+        <v>0.021</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6813</v>
+        <v>0.7054</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0379</v>
+        <v>0.0214</v>
       </c>
       <c r="N8" t="n">
-        <v>0.6745</v>
+        <v>0.6916</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0435</v>
+        <v>0.0355</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1538</v>
+        <v>0.1468</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.0107</v>
+        <v>0.0105</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6601</v>
+        <v>0.7004</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0106</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>0.7725</v>
+        <v>0.8046</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0365</v>
+        <v>0.0217</v>
       </c>
       <c r="V8" t="n">
-        <v>9.2697</v>
+        <v>9.655099999999999</v>
       </c>
       <c r="W8" t="n">
-        <v>0.4384</v>
+        <v>0.2603</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -4816,12 +4816,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -4998,74 +4998,74 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>34.3428</v>
+        <v>34.5481</v>
       </c>
       <c r="C2" t="n">
-        <v>1.5119</v>
+        <v>0.9897</v>
       </c>
       <c r="D2" t="n">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="E2" t="n">
         <v>4.4721</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0297</v>
+        <v>0.0295</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0004</v>
+        <v>0.0003</v>
       </c>
       <c r="H2" t="n">
-        <v>0.732</v>
+        <v>0.768</v>
       </c>
       <c r="I2" t="n">
-        <v>0.06569999999999999</v>
+        <v>0.0622</v>
       </c>
       <c r="J2" t="n">
-        <v>0.635</v>
+        <v>0.6473</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0116</v>
+        <v>0.0132</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6357</v>
+        <v>0.6477000000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0121</v>
+        <v>0.0141</v>
       </c>
       <c r="N2" t="n">
-        <v>0.6252</v>
+        <v>0.6363</v>
       </c>
       <c r="O2" t="n">
-        <v>0.017</v>
+        <v>0.0194</v>
       </c>
       <c r="P2" t="n">
-        <v>0.1636</v>
+        <v>0.1662</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0038</v>
+        <v>0.0028</v>
       </c>
       <c r="R2" t="n">
-        <v>0.3904</v>
+        <v>0.4033</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0035</v>
+        <v>0.005</v>
       </c>
       <c r="T2" t="n">
-        <v>0.4894</v>
+        <v>0.509</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0073</v>
+        <v>0.0021</v>
       </c>
       <c r="V2" t="n">
-        <v>2.9362</v>
+        <v>3.0537</v>
       </c>
       <c r="W2" t="n">
-        <v>0.0437</v>
+        <v>0.0127</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -5080,12 +5080,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -5101,74 +5101,74 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>46.792</v>
+        <v>51.6329</v>
       </c>
       <c r="C3" t="n">
-        <v>1.1624</v>
+        <v>2.3252</v>
       </c>
       <c r="D3" t="n">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>6.1237</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1496</v>
+        <v>0.1573</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0022</v>
+        <v>0.0015</v>
       </c>
       <c r="H3" t="n">
-        <v>1.848</v>
+        <v>1.864</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0179</v>
+        <v>0.0537</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7049</v>
+        <v>0.7454</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0499</v>
+        <v>0.0256</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7071</v>
+        <v>0.7486</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0511</v>
+        <v>0.0257</v>
       </c>
       <c r="N3" t="n">
-        <v>0.7009</v>
+        <v>0.7379</v>
       </c>
       <c r="O3" t="n">
-        <v>0.052</v>
+        <v>0.0216</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2216</v>
+        <v>0.2221</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0296</v>
+        <v>0.0221</v>
       </c>
       <c r="R3" t="n">
-        <v>0.4774</v>
+        <v>0.504</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0306</v>
+        <v>0.0252</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8331</v>
+        <v>0.8585</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0373</v>
+        <v>0.0332</v>
       </c>
       <c r="V3" t="n">
-        <v>4.9987</v>
+        <v>5.1512</v>
       </c>
       <c r="W3" t="n">
-        <v>0.2236</v>
+        <v>0.1992</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -5204,74 +5204,74 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>43.1076</v>
+        <v>46.0636</v>
       </c>
       <c r="C4" t="n">
-        <v>1.4915</v>
+        <v>2.4588</v>
       </c>
       <c r="D4" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="E4" t="n">
-        <v>4.1833</v>
+        <v>5.7009</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1246</v>
+        <v>0.1303</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0021</v>
+        <v>0.0022</v>
       </c>
       <c r="H4" t="n">
-        <v>0.846</v>
+        <v>0.862</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0219</v>
+        <v>0.0179</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6379</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>0.036</v>
+        <v>0.0439</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6391</v>
+        <v>0.6859</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0357</v>
+        <v>0.0447</v>
       </c>
       <c r="N4" t="n">
-        <v>0.6155</v>
+        <v>0.6525</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0452</v>
+        <v>0.0489</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2154</v>
+        <v>0.2226</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.024</v>
+        <v>0.0273</v>
       </c>
       <c r="R4" t="n">
-        <v>0.4795</v>
+        <v>0.492</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0072</v>
+        <v>0.0036</v>
       </c>
       <c r="T4" t="n">
-        <v>1.0407</v>
+        <v>1.105</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0078</v>
+        <v>0.0359</v>
       </c>
       <c r="V4" t="n">
-        <v>6.2442</v>
+        <v>6.6298</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0469</v>
+        <v>0.2153</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -5286,12 +5286,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -5307,74 +5307,74 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>70.08110000000001</v>
+        <v>75.09399999999999</v>
       </c>
       <c r="C5" t="n">
-        <v>1.6965</v>
+        <v>2.8956</v>
       </c>
       <c r="D5" t="n">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="E5" t="n">
-        <v>2.7386</v>
+        <v>4.1833</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2913</v>
+        <v>0.2952</v>
       </c>
       <c r="G5" t="n">
-        <v>0.002</v>
+        <v>0.0014</v>
       </c>
       <c r="H5" t="n">
-        <v>6.48</v>
+        <v>6.448</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>0.0179</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6812</v>
+        <v>0.7035</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0287</v>
+        <v>0.0429</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6824</v>
+        <v>0.7052</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0286</v>
+        <v>0.043</v>
       </c>
       <c r="N5" t="n">
-        <v>0.6072</v>
+        <v>0.5599</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0269</v>
+        <v>0.1397</v>
       </c>
       <c r="P5" t="n">
-        <v>0.3282</v>
+        <v>0.3623</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0243</v>
+        <v>0.0034</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9107</v>
+        <v>0.916</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0321</v>
+        <v>0.0419</v>
       </c>
       <c r="T5" t="n">
-        <v>2.1031</v>
+        <v>2.211</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0288</v>
+        <v>0.0273</v>
       </c>
       <c r="V5" t="n">
-        <v>12.6187</v>
+        <v>13.2662</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1728</v>
+        <v>0.1639</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -5389,12 +5389,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -5410,74 +5410,74 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>66.4803</v>
+        <v>64.6746</v>
       </c>
       <c r="C6" t="n">
-        <v>6.6995</v>
+        <v>2.5369</v>
       </c>
       <c r="D6" t="n">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="E6" t="n">
-        <v>13.8744</v>
+        <v>4.4721</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1632</v>
+        <v>0.1636</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0015</v>
+        <v>0.0003</v>
       </c>
       <c r="H6" t="n">
-        <v>5.706</v>
+        <v>5.736</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0329</v>
+        <v>0.065</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6064000000000001</v>
+        <v>0.6042</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0057</v>
+        <v>0.0027</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6064000000000001</v>
+        <v>0.6048</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0062</v>
+        <v>0.0018</v>
       </c>
       <c r="N6" t="n">
-        <v>0.5721000000000001</v>
+        <v>0.5894</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0374</v>
+        <v>0.0095</v>
       </c>
       <c r="P6" t="n">
-        <v>0.266</v>
+        <v>0.2765</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0051</v>
+        <v>0.0058</v>
       </c>
       <c r="R6" t="n">
-        <v>0.52</v>
+        <v>0.5245</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0611</v>
+        <v>0.0245</v>
       </c>
       <c r="T6" t="n">
-        <v>0.9744</v>
+        <v>1.0278</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0277</v>
+        <v>0.0354</v>
       </c>
       <c r="V6" t="n">
-        <v>5.8462</v>
+        <v>6.1668</v>
       </c>
       <c r="W6" t="n">
-        <v>0.1665</v>
+        <v>0.2123</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -5492,12 +5492,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -5513,74 +5513,74 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>45.4699</v>
+        <v>48.6507</v>
       </c>
       <c r="C7" t="n">
-        <v>4.6075</v>
+        <v>3.4735</v>
       </c>
       <c r="D7" t="n">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E7" t="n">
-        <v>10.9545</v>
+        <v>8.660299999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1024</v>
+        <v>0.104</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0008</v>
+        <v>0.001</v>
       </c>
       <c r="H7" t="n">
-        <v>3.42</v>
+        <v>3.412</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0644</v>
+        <v>0.07530000000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5907</v>
+        <v>0.6052</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0461</v>
+        <v>0.0074</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5884</v>
+        <v>0.6046</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0496</v>
+        <v>0.0071</v>
       </c>
       <c r="N7" t="n">
-        <v>0.5588</v>
+        <v>0.5503</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0677</v>
+        <v>0.1222</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1726</v>
+        <v>0.1826</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0023</v>
+        <v>0.0056</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3618</v>
+        <v>0.3664</v>
       </c>
       <c r="S7" t="n">
-        <v>0.028</v>
+        <v>0.0354</v>
       </c>
       <c r="T7" t="n">
-        <v>0.554</v>
+        <v>0.5762</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0049</v>
+        <v>0.0047</v>
       </c>
       <c r="V7" t="n">
-        <v>3.324</v>
+        <v>3.4575</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0293</v>
+        <v>0.0279</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -5616,74 +5616,74 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>38.7503</v>
+        <v>44.7079</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1758</v>
+        <v>2.7248</v>
       </c>
       <c r="D8" t="n">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>8.3666</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1025</v>
+        <v>0.1048</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0009</v>
+        <v>0.0007</v>
       </c>
       <c r="H8" t="n">
-        <v>2.204</v>
+        <v>2.256</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0167</v>
+        <v>0.1048</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5289</v>
+        <v>0.6125</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1141</v>
+        <v>0.0053</v>
       </c>
       <c r="L8" t="n">
-        <v>0.528</v>
+        <v>0.6127</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1152</v>
+        <v>0.0069</v>
       </c>
       <c r="N8" t="n">
-        <v>0.5132</v>
+        <v>0.6104000000000001</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1326</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1567</v>
+        <v>0.164</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.0044</v>
+        <v>0.0037</v>
       </c>
       <c r="R8" t="n">
-        <v>0.3358</v>
+        <v>0.349</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0237</v>
+        <v>0.0236</v>
       </c>
       <c r="T8" t="n">
-        <v>0.633</v>
+        <v>0.6497000000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0271</v>
+        <v>0.0339</v>
       </c>
       <c r="V8" t="n">
-        <v>3.7982</v>
+        <v>3.8979</v>
       </c>
       <c r="W8" t="n">
-        <v>0.1628</v>
+        <v>0.2032</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -5698,12 +5698,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -5880,74 +5880,74 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>34.7045</v>
+        <v>37.1667</v>
       </c>
       <c r="C2" t="n">
-        <v>1.3719</v>
+        <v>0.5542</v>
       </c>
       <c r="D2" t="n">
         <v>107</v>
       </c>
       <c r="E2" t="n">
-        <v>4.4721</v>
+        <v>2.7386</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0303</v>
+        <v>0.0307</v>
       </c>
       <c r="G2" t="n">
         <v>0.0002</v>
       </c>
       <c r="H2" t="n">
-        <v>0.778</v>
+        <v>0.786</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0179</v>
+        <v>0.0219</v>
       </c>
       <c r="J2" t="n">
-        <v>0.6388</v>
+        <v>0.6477000000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01</v>
+        <v>0.0112</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5964</v>
+        <v>0.5951</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0187</v>
+        <v>0.0139</v>
       </c>
       <c r="N2" t="n">
-        <v>0.6099</v>
+        <v>0.6092</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0195</v>
+        <v>0.0135</v>
       </c>
       <c r="P2" t="n">
-        <v>0.1896</v>
+        <v>0.1935</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0048</v>
+        <v>0.0055</v>
       </c>
       <c r="R2" t="n">
-        <v>0.5472</v>
+        <v>0.5492</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0156</v>
+        <v>0.0146</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6384</v>
+        <v>0.6689000000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0112</v>
+        <v>0.0108</v>
       </c>
       <c r="V2" t="n">
-        <v>3.8304</v>
+        <v>4.0133</v>
       </c>
       <c r="W2" t="n">
-        <v>0.067</v>
+        <v>0.06510000000000001</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -5962,12 +5962,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -5983,74 +5983,74 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>52.0239</v>
+        <v>54.8965</v>
       </c>
       <c r="C3" t="n">
-        <v>2.9845</v>
+        <v>2.7968</v>
       </c>
       <c r="D3" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E3" t="n">
-        <v>6.5192</v>
+        <v>5.4772</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1544</v>
+        <v>0.1585</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0012</v>
+        <v>0.0029</v>
       </c>
       <c r="H3" t="n">
-        <v>1.89</v>
+        <v>1.876</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0539</v>
+        <v>0.07770000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6546</v>
+        <v>0.643</v>
       </c>
       <c r="K3" t="n">
-        <v>0.029</v>
+        <v>0.0234</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5916</v>
+        <v>0.5833</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0225</v>
+        <v>0.0188</v>
       </c>
       <c r="N3" t="n">
-        <v>0.603</v>
+        <v>0.5893</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0265</v>
+        <v>0.0222</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2379</v>
+        <v>0.2554</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0302</v>
+        <v>0.0268</v>
       </c>
       <c r="R3" t="n">
-        <v>0.6446</v>
+        <v>0.6636</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0226</v>
+        <v>0.0271</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9594</v>
+        <v>0.9852</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0453</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="V3" t="n">
-        <v>5.7562</v>
+        <v>5.9114</v>
       </c>
       <c r="W3" t="n">
-        <v>0.2718</v>
+        <v>0.049</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -6065,12 +6065,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -6086,74 +6086,74 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>45.6709</v>
+        <v>49.7985</v>
       </c>
       <c r="C4" t="n">
-        <v>2.3077</v>
+        <v>1.3219</v>
       </c>
       <c r="D4" t="n">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="E4" t="n">
-        <v>6.5192</v>
+        <v>4.1833</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1248</v>
+        <v>0.1315</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0021</v>
+        <v>0.0011</v>
       </c>
       <c r="H4" t="n">
-        <v>0.862</v>
+        <v>0.874</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0455</v>
+        <v>0.055</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5324</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0219</v>
+        <v>0.0541</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4698</v>
+        <v>0.4865</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0245</v>
+        <v>0.0585</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3901</v>
+        <v>0.3961</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0638</v>
+        <v>0.0187</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2335</v>
+        <v>0.2203</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0196</v>
+        <v>0.0284</v>
       </c>
       <c r="R4" t="n">
-        <v>0.7851</v>
+        <v>0.8308</v>
       </c>
       <c r="S4" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.0307</v>
       </c>
       <c r="T4" t="n">
-        <v>1.3015</v>
+        <v>1.3844</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0116</v>
+        <v>0.0118</v>
       </c>
       <c r="V4" t="n">
-        <v>7.809</v>
+        <v>8.3066</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0697</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -6168,12 +6168,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -6189,74 +6189,74 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>72.8121</v>
+        <v>77.0663</v>
       </c>
       <c r="C5" t="n">
-        <v>2.7348</v>
+        <v>4.087</v>
       </c>
       <c r="D5" t="n">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="E5" t="n">
-        <v>4.4721</v>
+        <v>4.1833</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2899</v>
+        <v>0.2974</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0019</v>
+        <v>0.0018</v>
       </c>
       <c r="H5" t="n">
-        <v>6.472</v>
+        <v>6.456</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0179</v>
+        <v>0.0219</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5623</v>
+        <v>0.6011</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0389</v>
+        <v>0.0147</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4916</v>
+        <v>0.5246</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0493</v>
+        <v>0.0244</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2688</v>
+        <v>0.3257</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1</v>
+        <v>0.0121</v>
       </c>
       <c r="P5" t="n">
-        <v>0.3576</v>
+        <v>0.3543</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0271</v>
+        <v>0.031</v>
       </c>
       <c r="R5" t="n">
-        <v>1.0463</v>
+        <v>1.1077</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0281</v>
+        <v>0.0152</v>
       </c>
       <c r="T5" t="n">
-        <v>2.2593</v>
+        <v>2.3701</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0351</v>
+        <v>0.0325</v>
       </c>
       <c r="V5" t="n">
-        <v>13.5557</v>
+        <v>14.2206</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2107</v>
+        <v>0.1951</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -6271,12 +6271,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -6292,74 +6292,74 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>72.7927</v>
+        <v>86.33320000000001</v>
       </c>
       <c r="C6" t="n">
-        <v>3.6074</v>
+        <v>14.1691</v>
       </c>
       <c r="D6" t="n">
-        <v>106</v>
+        <v>124</v>
       </c>
       <c r="E6" t="n">
-        <v>4.4721</v>
+        <v>19.3649</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1643</v>
+        <v>0.1655</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0009</v>
+        <v>0.0011</v>
       </c>
       <c r="H6" t="n">
-        <v>5.722</v>
+        <v>5.732</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0295</v>
+        <v>0.0045</v>
       </c>
       <c r="J6" t="n">
-        <v>0.424</v>
+        <v>0.4962</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0196</v>
+        <v>0.0658</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4184</v>
+        <v>0.4749</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0244</v>
+        <v>0.0575</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3999</v>
+        <v>0.4443</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0441</v>
+        <v>0.0546</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2834</v>
+        <v>0.3142</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0017</v>
+        <v>0.0266</v>
       </c>
       <c r="R6" t="n">
-        <v>0.648</v>
+        <v>0.6629</v>
       </c>
       <c r="S6" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.0111</v>
       </c>
       <c r="T6" t="n">
-        <v>1.1111</v>
+        <v>1.1522</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0295</v>
+        <v>0.0269</v>
       </c>
       <c r="V6" t="n">
-        <v>6.6668</v>
+        <v>6.9134</v>
       </c>
       <c r="W6" t="n">
-        <v>0.177</v>
+        <v>0.1616</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -6374,12 +6374,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -6395,74 +6395,74 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>47.5957</v>
+        <v>61.8054</v>
       </c>
       <c r="C7" t="n">
-        <v>1.7792</v>
+        <v>8.3467</v>
       </c>
       <c r="D7" t="n">
-        <v>106</v>
+        <v>125</v>
       </c>
       <c r="E7" t="n">
-        <v>2.7386</v>
+        <v>17.1026</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1026</v>
+        <v>0.1049</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0012</v>
+        <v>0.001</v>
       </c>
       <c r="H7" t="n">
-        <v>3.382</v>
+        <v>3.398</v>
       </c>
       <c r="I7" t="n">
-        <v>0.039</v>
+        <v>0.0955</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4602</v>
+        <v>0.4998</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0454</v>
+        <v>0.0598</v>
       </c>
       <c r="L7" t="n">
-        <v>0.4423</v>
+        <v>0.4795</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0368</v>
+        <v>0.0498</v>
       </c>
       <c r="N7" t="n">
-        <v>0.4263</v>
+        <v>0.4555</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0325</v>
+        <v>0.0444</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1949</v>
+        <v>0.2062</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0032</v>
+        <v>0.0041</v>
       </c>
       <c r="R7" t="n">
-        <v>0.4968</v>
+        <v>0.4984</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0295</v>
+        <v>0.0275</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6963</v>
+        <v>0.731</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0071</v>
+        <v>0.0056</v>
       </c>
       <c r="V7" t="n">
-        <v>4.1777</v>
+        <v>4.3858</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0427</v>
+        <v>0.0337</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -6477,12 +6477,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -6498,74 +6498,74 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>43.3466</v>
+        <v>50.2461</v>
       </c>
       <c r="C8" t="n">
-        <v>1.7102</v>
+        <v>11.987</v>
       </c>
       <c r="D8" t="n">
-        <v>107</v>
+        <v>122</v>
       </c>
       <c r="E8" t="n">
-        <v>4.4721</v>
+        <v>29.2831</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1033</v>
+        <v>0.1046</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0022</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>2.238</v>
+        <v>2.242</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0205</v>
+        <v>0.0438</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4078</v>
+        <v>0.4517</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0056</v>
+        <v>0.1063</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3757</v>
+        <v>0.4076</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0182</v>
+        <v>0.0987</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3631</v>
+        <v>0.3974</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0124</v>
+        <v>0.0771</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1755</v>
+        <v>0.1812</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.0056</v>
+        <v>0.003</v>
       </c>
       <c r="R8" t="n">
-        <v>0.4876</v>
+        <v>0.5088</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0081</v>
+        <v>0.0101</v>
       </c>
       <c r="T8" t="n">
-        <v>0.7589</v>
+        <v>0.7991</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0298</v>
+        <v>0.0381</v>
       </c>
       <c r="V8" t="n">
-        <v>4.5536</v>
+        <v>4.7943</v>
       </c>
       <c r="W8" t="n">
-        <v>0.1789</v>
+        <v>0.2288</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -6580,12 +6580,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">

--- a/tests/perf_v2/perf_history/v2.5/semantic_segmentation/SEMANTIC_SEGMENTATION-aggregated.xlsx
+++ b/tests/perf_v2/perf_history/v2.5/semantic_segmentation/SEMANTIC_SEGMENTATION-aggregated.xlsx
@@ -588,52 +588,52 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>249.8699</v>
+        <v>264.3972</v>
       </c>
       <c r="C2" t="n">
-        <v>88.886</v>
+        <v>114.3917</v>
       </c>
       <c r="D2" t="n">
-        <v>28.8</v>
+        <v>30.6</v>
       </c>
       <c r="E2" t="n">
-        <v>10.7564</v>
+        <v>13.8311</v>
       </c>
       <c r="F2" t="n">
         <v>0.0442</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0003</v>
+        <v>0.0001</v>
       </c>
       <c r="H2" t="n">
-        <v>2.154</v>
+        <v>2.202</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4724</v>
+        <v>0.5148</v>
       </c>
       <c r="J2" t="n">
-        <v>0.7922</v>
+        <v>0.7925</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0023</v>
+        <v>0.0017</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7917999999999999</v>
+        <v>0.7919</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0021</v>
+        <v>0.0016</v>
       </c>
       <c r="N2" t="n">
-        <v>0.7911</v>
+        <v>0.7913</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0024</v>
+        <v>0.002</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0092</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0005</v>
+        <v>0.0002</v>
       </c>
       <c r="R2" t="n">
         <v>0.0861</v>
@@ -642,16 +642,16 @@
         <v>0.0009</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0567</v>
+        <v>0.0574</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0009</v>
+        <v>0.0013</v>
       </c>
       <c r="V2" t="n">
-        <v>15.8301</v>
+        <v>16.0225</v>
       </c>
       <c r="W2" t="n">
-        <v>0.2404</v>
+        <v>0.3737</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -691,70 +691,70 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1449.2066</v>
+        <v>1483.4535</v>
       </c>
       <c r="C3" t="n">
-        <v>143.8108</v>
+        <v>131.0524</v>
       </c>
       <c r="D3" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E3" t="n">
-        <v>5.7879</v>
+        <v>5.1962</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1563</v>
+        <v>0.1572</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0004</v>
+        <v>0.0008</v>
       </c>
       <c r="H3" t="n">
-        <v>2.834</v>
+        <v>2.842</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0391</v>
+        <v>0.0409</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7919</v>
+        <v>0.7923</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0029</v>
+        <v>0.0037</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7892</v>
+        <v>0.7899</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0031</v>
+        <v>0.0036</v>
       </c>
       <c r="N3" t="n">
-        <v>0.7842</v>
+        <v>0.7874</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0027</v>
+        <v>0.0032</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0141</v>
+        <v>0.0142</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0008</v>
+        <v>0.0009</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0499</v>
+        <v>0.0498</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0011</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0598</v>
+        <v>0.0606</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.0015</v>
       </c>
       <c r="V3" t="n">
-        <v>16.6749</v>
+        <v>16.8978</v>
       </c>
       <c r="W3" t="n">
-        <v>0.1727</v>
+        <v>0.4053</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -794,70 +794,70 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1243.1934</v>
+        <v>1339.6073</v>
       </c>
       <c r="C4" t="n">
-        <v>186.2928</v>
+        <v>306.1477</v>
       </c>
       <c r="D4" t="n">
-        <v>57.6</v>
+        <v>62.4</v>
       </c>
       <c r="E4" t="n">
-        <v>8.848699999999999</v>
+        <v>14.2759</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1342</v>
+        <v>0.1337</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0009</v>
+        <v>0.0007</v>
       </c>
       <c r="H4" t="n">
-        <v>1.72</v>
+        <v>1.714</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0187</v>
+        <v>0.027</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7638</v>
+        <v>0.7696</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0064</v>
+        <v>0.0124</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7621</v>
+        <v>0.7677</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0063</v>
+        <v>0.0125</v>
       </c>
       <c r="N4" t="n">
-        <v>0.7155</v>
+        <v>0.7328</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0135</v>
+        <v>0.0246</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0121</v>
+        <v>0.012</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0004</v>
+        <v>0.0005</v>
       </c>
       <c r="R4" t="n">
         <v>0.0529</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0009</v>
+        <v>0.0004</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0703</v>
+        <v>0.0704</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0012</v>
+        <v>0.0022</v>
       </c>
       <c r="V4" t="n">
-        <v>19.6224</v>
+        <v>19.644</v>
       </c>
       <c r="W4" t="n">
-        <v>0.3223</v>
+        <v>0.608</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -897,70 +897,70 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2996.1506</v>
+        <v>2795.6988</v>
       </c>
       <c r="C5" t="n">
-        <v>411.8072</v>
+        <v>974.4056</v>
       </c>
       <c r="D5" t="n">
-        <v>58.8</v>
+        <v>54.8</v>
       </c>
       <c r="E5" t="n">
-        <v>8.167</v>
+        <v>19.5115</v>
       </c>
       <c r="F5" t="n">
-        <v>0.332</v>
+        <v>0.3322</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0005</v>
+        <v>0.0007</v>
       </c>
       <c r="H5" t="n">
-        <v>8.901999999999999</v>
+        <v>8.882</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0396</v>
+        <v>0.0259</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7952</v>
+        <v>0.7871</v>
       </c>
       <c r="K5" t="n">
-        <v>0.004</v>
+        <v>0.0229</v>
       </c>
       <c r="L5" t="n">
-        <v>0.792</v>
+        <v>0.7841</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0039</v>
+        <v>0.0228</v>
       </c>
       <c r="N5" t="n">
-        <v>0.433</v>
+        <v>0.6027</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1814</v>
+        <v>0.0638</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0217</v>
+        <v>0.0212</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.0001</v>
       </c>
       <c r="R5" t="n">
-        <v>0.1216</v>
+        <v>0.1212</v>
       </c>
       <c r="S5" t="n">
         <v>0.0009</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1317</v>
+        <v>0.1316</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0011</v>
+        <v>0.0012</v>
       </c>
       <c r="V5" t="n">
-        <v>36.7305</v>
+        <v>36.7279</v>
       </c>
       <c r="W5" t="n">
-        <v>0.3067</v>
+        <v>0.3219</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1000,70 +1000,70 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2361.209</v>
+        <v>1895.3292</v>
       </c>
       <c r="C6" t="n">
-        <v>376.0096</v>
+        <v>274.892</v>
       </c>
       <c r="D6" t="n">
-        <v>73.59999999999999</v>
+        <v>58.8</v>
       </c>
       <c r="E6" t="n">
-        <v>11.8659</v>
+        <v>8.642899999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2005</v>
+        <v>0.201</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0001</v>
+        <v>0.0002</v>
       </c>
       <c r="H6" t="n">
-        <v>7.51</v>
+        <v>7.528</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0505</v>
+        <v>0.0585</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8250999999999999</v>
+        <v>0.8224</v>
       </c>
       <c r="K6" t="n">
-        <v>0.004</v>
+        <v>0.0051</v>
       </c>
       <c r="L6" t="n">
-        <v>0.8228</v>
+        <v>0.8202</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0036</v>
+        <v>0.0052</v>
       </c>
       <c r="N6" t="n">
-        <v>0.8197</v>
+        <v>0.8159</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0052</v>
+        <v>0.0059</v>
       </c>
       <c r="P6" t="n">
-        <v>0.016</v>
+        <v>0.0163</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0005</v>
+        <v>0.0007</v>
       </c>
       <c r="R6" t="n">
-        <v>0.09180000000000001</v>
+        <v>0.0922</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0013</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="T6" t="n">
-        <v>0.07240000000000001</v>
+        <v>0.0738</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="V6" t="n">
-        <v>20.1952</v>
+        <v>20.5828</v>
       </c>
       <c r="W6" t="n">
-        <v>0.1523</v>
+        <v>0.2904</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1103,70 +1103,70 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1248.1917</v>
+        <v>1244.5198</v>
       </c>
       <c r="C7" t="n">
-        <v>253.4658</v>
+        <v>279.1601</v>
       </c>
       <c r="D7" t="n">
-        <v>60.6</v>
+        <v>60.8</v>
       </c>
       <c r="E7" t="n">
-        <v>12.341</v>
+        <v>14.1669</v>
       </c>
       <c r="F7" t="n">
         <v>0.1264</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.0012</v>
       </c>
       <c r="H7" t="n">
-        <v>5.038</v>
+        <v>5.028</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0653</v>
+        <v>0.1397</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8107</v>
+        <v>0.8096</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0039</v>
+        <v>0.0073</v>
       </c>
       <c r="L7" t="n">
-        <v>0.8088</v>
+        <v>0.8076</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0042</v>
+        <v>0.0071</v>
       </c>
       <c r="N7" t="n">
-        <v>0.8064</v>
+        <v>0.8048</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0047</v>
+        <v>0.0075</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0112</v>
+        <v>0.0114</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0002</v>
+        <v>0.0004</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0587</v>
+        <v>0.0578</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0016</v>
+        <v>0.0011</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0506</v>
+        <v>0.0491</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0031</v>
+        <v>0.0005</v>
       </c>
       <c r="V7" t="n">
-        <v>14.1276</v>
+        <v>13.7027</v>
       </c>
       <c r="W7" t="n">
-        <v>0.8779</v>
+        <v>0.1519</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1206,70 +1206,70 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1429.2097</v>
+        <v>1442.0677</v>
       </c>
       <c r="C8" t="n">
-        <v>106.1124</v>
+        <v>296.1351</v>
       </c>
       <c r="D8" t="n">
-        <v>77.59999999999999</v>
+        <v>78</v>
       </c>
       <c r="E8" t="n">
-        <v>5.7706</v>
+        <v>16.8819</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1143</v>
+        <v>0.1151</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0002</v>
+        <v>0.0014</v>
       </c>
       <c r="H8" t="n">
-        <v>3.806</v>
+        <v>3.724</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0956</v>
+        <v>0.08989999999999999</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8002</v>
+        <v>0.7996</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0027</v>
+        <v>0.0042</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7984</v>
+        <v>0.7978</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0027</v>
+        <v>0.0039</v>
       </c>
       <c r="N8" t="n">
-        <v>0.7963</v>
+        <v>0.7961</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0035</v>
+        <v>0.0047</v>
       </c>
       <c r="P8" t="n">
         <v>0.009900000000000001</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.0003</v>
+        <v>0.0004</v>
       </c>
       <c r="R8" t="n">
-        <v>0.0452</v>
+        <v>0.0447</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.0009</v>
       </c>
       <c r="T8" t="n">
-        <v>0.047</v>
+        <v>0.0471</v>
       </c>
       <c r="U8" t="n">
         <v>0.0009</v>
       </c>
       <c r="V8" t="n">
-        <v>13.1105</v>
+        <v>13.1534</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2492</v>
+        <v>0.254</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1470,70 +1470,70 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>24.6398</v>
+        <v>90.389</v>
       </c>
       <c r="C2" t="n">
-        <v>9.434900000000001</v>
+        <v>14.5994</v>
       </c>
       <c r="D2" t="n">
-        <v>12.4</v>
+        <v>51.2</v>
       </c>
       <c r="E2" t="n">
-        <v>5.3666</v>
+        <v>8.8994</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0543</v>
+        <v>0.0549</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0002</v>
+        <v>0.0004</v>
       </c>
       <c r="H2" t="n">
-        <v>1.312</v>
+        <v>1.676</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1381</v>
+        <v>0.1205</v>
       </c>
       <c r="J2" t="n">
-        <v>0.5758</v>
+        <v>0.6468</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0315</v>
+        <v>0.0022</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5741000000000001</v>
+        <v>0.6443</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0313</v>
+        <v>0.0021</v>
       </c>
       <c r="N2" t="n">
-        <v>0.5756</v>
+        <v>0.6467000000000001</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0343</v>
+        <v>0.002</v>
       </c>
       <c r="P2" t="n">
         <v>0.0281</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0007</v>
+        <v>0.0008</v>
       </c>
       <c r="R2" t="n">
-        <v>0.2342</v>
+        <v>0.2373</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0022</v>
+        <v>0.0026</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2323</v>
+        <v>0.2305</v>
       </c>
       <c r="U2" t="n">
         <v>0.0036</v>
       </c>
       <c r="V2" t="n">
-        <v>11.6158</v>
+        <v>11.5252</v>
       </c>
       <c r="W2" t="n">
-        <v>0.1776</v>
+        <v>0.179</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1573,70 +1573,70 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>114.1059</v>
+        <v>277.8922</v>
       </c>
       <c r="C3" t="n">
-        <v>12.1216</v>
+        <v>102.6702</v>
       </c>
       <c r="D3" t="n">
-        <v>28.6</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>3.2863</v>
+        <v>27.2819</v>
       </c>
       <c r="F3" t="n">
-        <v>0.161</v>
+        <v>0.1617</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0005</v>
+        <v>0.0008</v>
       </c>
       <c r="H3" t="n">
-        <v>2.906</v>
+        <v>2.908</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0207</v>
+        <v>0.0217</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4226</v>
+        <v>0.4632</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0169</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4217</v>
+        <v>0.4626</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0172</v>
+        <v>0.0098</v>
       </c>
       <c r="N3" t="n">
-        <v>0.4172</v>
+        <v>0.4553</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0182</v>
+        <v>0.0131</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0406</v>
+        <v>0.0379</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0034</v>
+        <v>0.0027</v>
       </c>
       <c r="R3" t="n">
-        <v>0.2456</v>
+        <v>0.2379</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0094</v>
+        <v>0.0025</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3028</v>
+        <v>0.3108</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0132</v>
+        <v>0.0124</v>
       </c>
       <c r="V3" t="n">
-        <v>15.1403</v>
+        <v>15.5382</v>
       </c>
       <c r="W3" t="n">
-        <v>0.6611</v>
+        <v>0.6176</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1676,70 +1676,70 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>105.5346</v>
+        <v>258.1688</v>
       </c>
       <c r="C4" t="n">
-        <v>17.3115</v>
+        <v>41.7336</v>
       </c>
       <c r="D4" t="n">
-        <v>31</v>
+        <v>78.8</v>
       </c>
       <c r="E4" t="n">
-        <v>5.1962</v>
+        <v>13.0077</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1345</v>
+        <v>0.1332</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0015</v>
+        <v>0.0002</v>
       </c>
       <c r="H4" t="n">
-        <v>1.52</v>
+        <v>1.532</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0951</v>
+        <v>0.123</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3992</v>
+        <v>0.4498</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0219</v>
+        <v>0.0102</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3987</v>
+        <v>0.4489</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0218</v>
+        <v>0.0101</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3433</v>
+        <v>0.391</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0441</v>
+        <v>0.0246</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0319</v>
+        <v>0.0332</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0009</v>
+        <v>0.0024</v>
       </c>
       <c r="R4" t="n">
-        <v>0.4001</v>
+        <v>0.4012</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0029</v>
+        <v>0.0044</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4711</v>
+        <v>0.4845</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0067</v>
+        <v>0.0126</v>
       </c>
       <c r="V4" t="n">
-        <v>23.5566</v>
+        <v>24.2273</v>
       </c>
       <c r="W4" t="n">
-        <v>0.3367</v>
+        <v>0.6294</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1779,70 +1779,70 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>159.4236</v>
+        <v>698.3392</v>
       </c>
       <c r="C5" t="n">
-        <v>62.7364</v>
+        <v>28.6936</v>
       </c>
       <c r="D5" t="n">
-        <v>20.8</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>8.642899999999999</v>
+        <v>3.9115</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3313</v>
+        <v>0.3316</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0017</v>
+        <v>0.0008</v>
       </c>
       <c r="H5" t="n">
-        <v>8.914</v>
+        <v>8.9</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0796</v>
+        <v>0.0224</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3572</v>
+        <v>0.4931</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0629</v>
+        <v>0.0083</v>
       </c>
       <c r="L5" t="n">
-        <v>0.357</v>
+        <v>0.4924</v>
       </c>
       <c r="M5" t="n">
-        <v>0.06270000000000001</v>
+        <v>0.0081</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2548</v>
+        <v>0.2218</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0464</v>
+        <v>0.0437</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0562</v>
+        <v>0.0586</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0033</v>
+        <v>0.003</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3426</v>
+        <v>0.3464</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0071</v>
+        <v>0.0083</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4856</v>
+        <v>0.486</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0028</v>
+        <v>0.0058</v>
       </c>
       <c r="V5" t="n">
-        <v>24.2822</v>
+        <v>24.3</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1381</v>
+        <v>0.2894</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1882,70 +1882,70 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>139.2863</v>
+        <v>708.6759</v>
       </c>
       <c r="C6" t="n">
-        <v>42.8366</v>
+        <v>217.883</v>
       </c>
       <c r="D6" t="n">
-        <v>26.8</v>
+        <v>143.6</v>
       </c>
       <c r="E6" t="n">
-        <v>8.642899999999999</v>
+        <v>44.7694</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2053</v>
+        <v>0.2054</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0004</v>
+        <v>0.0007</v>
       </c>
       <c r="H6" t="n">
-        <v>7.672</v>
+        <v>7.808</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0939</v>
+        <v>0.1018</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4192</v>
+        <v>0.6282</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0781</v>
+        <v>0.0629</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4186</v>
+        <v>0.626</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0781</v>
+        <v>0.0623</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3585</v>
+        <v>0.6141</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0505</v>
+        <v>0.0619</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0474</v>
+        <v>0.0477</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0031</v>
+        <v>0.0029</v>
       </c>
       <c r="R6" t="n">
-        <v>0.2666</v>
+        <v>0.2737</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0123</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2988</v>
+        <v>0.3034</v>
       </c>
       <c r="U6" t="n">
         <v>0.0045</v>
       </c>
       <c r="V6" t="n">
-        <v>14.9412</v>
+        <v>15.1677</v>
       </c>
       <c r="W6" t="n">
-        <v>0.2246</v>
+        <v>0.2245</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1985,70 +1985,70 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>120.2489</v>
+        <v>379.9241</v>
       </c>
       <c r="C7" t="n">
-        <v>47.1057</v>
+        <v>46.5829</v>
       </c>
       <c r="D7" t="n">
-        <v>36.4</v>
+        <v>119</v>
       </c>
       <c r="E7" t="n">
-        <v>14.758</v>
+        <v>15</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1239</v>
+        <v>0.1245</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0002</v>
+        <v>0.0005</v>
       </c>
       <c r="H7" t="n">
-        <v>4.62</v>
+        <v>4.77</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1037</v>
+        <v>0.0274</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3826</v>
+        <v>0.5265</v>
       </c>
       <c r="K7" t="n">
-        <v>0.09909999999999999</v>
+        <v>0.0048</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3821</v>
+        <v>0.5253</v>
       </c>
       <c r="M7" t="n">
-        <v>0.09909999999999999</v>
+        <v>0.0049</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3798</v>
+        <v>0.5201</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0992</v>
+        <v>0.0073</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0314</v>
+        <v>0.033</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.003</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2246</v>
+        <v>0.2208</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0072</v>
+        <v>0.0027</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2394</v>
+        <v>0.244</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0064</v>
+        <v>0.0065</v>
       </c>
       <c r="V7" t="n">
-        <v>11.9687</v>
+        <v>12.1982</v>
       </c>
       <c r="W7" t="n">
-        <v>0.3201</v>
+        <v>0.327</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -2088,70 +2088,70 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>161.4605</v>
+        <v>353.1456</v>
       </c>
       <c r="C8" t="n">
-        <v>44.8127</v>
+        <v>61.2972</v>
       </c>
       <c r="D8" t="n">
-        <v>55.6</v>
+        <v>124.4</v>
       </c>
       <c r="E8" t="n">
-        <v>16.0717</v>
+        <v>22.1878</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1126</v>
+        <v>0.1127</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0009</v>
+        <v>0.0004</v>
       </c>
       <c r="H8" t="n">
-        <v>3.464</v>
+        <v>3.494</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0241</v>
+        <v>0.0358</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3997</v>
+        <v>0.4946</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0641</v>
+        <v>0.0134</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3995</v>
+        <v>0.4939</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0641</v>
+        <v>0.0135</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3828</v>
+        <v>0.4824</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0536</v>
+        <v>0.0185</v>
       </c>
       <c r="P8" t="n">
-        <v>0.0283</v>
+        <v>0.0279</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.0003</v>
       </c>
       <c r="R8" t="n">
-        <v>0.2192</v>
+        <v>0.2157</v>
       </c>
       <c r="S8" t="n">
         <v>0.0022</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2494</v>
+        <v>0.2437</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0044</v>
+        <v>0.0075</v>
       </c>
       <c r="V8" t="n">
-        <v>12.4684</v>
+        <v>12.1835</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2214</v>
+        <v>0.3753</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -2352,10 +2352,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>177.0713</v>
+        <v>176.0062</v>
       </c>
       <c r="C2" t="n">
-        <v>40.2343</v>
+        <v>38.8639</v>
       </c>
       <c r="D2" t="n">
         <v>20.8</v>
@@ -2364,58 +2364,58 @@
         <v>4.9699</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0576</v>
+        <v>0.0577</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0002</v>
+        <v>0.0003</v>
       </c>
       <c r="H2" t="n">
-        <v>3.062</v>
+        <v>2.648</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2199</v>
+        <v>0.2994</v>
       </c>
       <c r="J2" t="n">
-        <v>0.8665</v>
+        <v>0.8661</v>
       </c>
       <c r="K2" t="n">
         <v>0.0045</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8649</v>
+        <v>0.8646</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0048</v>
+        <v>0.0047</v>
       </c>
       <c r="N2" t="n">
-        <v>0.8645</v>
+        <v>0.8643999999999999</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0056</v>
+        <v>0.0055</v>
       </c>
       <c r="P2" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.0104</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0001</v>
+        <v>0.002</v>
       </c>
       <c r="R2" t="n">
-        <v>0.1163</v>
+        <v>0.1181</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0014</v>
+        <v>0.0041</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0919</v>
+        <v>0.0948</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0017</v>
+        <v>0.0032</v>
       </c>
       <c r="V2" t="n">
-        <v>27.5844</v>
+        <v>28.4441</v>
       </c>
       <c r="W2" t="n">
-        <v>0.4961</v>
+        <v>0.958</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -2455,70 +2455,70 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1119.2089</v>
+        <v>1123.7968</v>
       </c>
       <c r="C3" t="n">
-        <v>242.9613</v>
+        <v>247.5455</v>
       </c>
       <c r="D3" t="n">
-        <v>62.6</v>
+        <v>63</v>
       </c>
       <c r="E3" t="n">
-        <v>14.0641</v>
+        <v>14.089</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1597</v>
+        <v>0.1592</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0014</v>
+        <v>0.0002</v>
       </c>
       <c r="H3" t="n">
-        <v>3.562</v>
+        <v>3.508</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1047</v>
+        <v>0.07920000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4549</v>
+        <v>0.4289</v>
       </c>
       <c r="K3" t="n">
-        <v>0.021</v>
+        <v>0.0165</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4519</v>
+        <v>0.4261</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0216</v>
+        <v>0.0167</v>
       </c>
       <c r="N3" t="n">
-        <v>0.4236</v>
+        <v>0.3819</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0192</v>
+        <v>0.0308</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0143</v>
+        <v>0.0147</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0005</v>
+        <v>0.0002</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0912</v>
+        <v>0.091</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0016</v>
+        <v>0.0012</v>
       </c>
       <c r="T3" t="n">
-        <v>0.099</v>
+        <v>0.0987</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0016</v>
+        <v>0.0019</v>
       </c>
       <c r="V3" t="n">
-        <v>29.6972</v>
+        <v>29.6036</v>
       </c>
       <c r="W3" t="n">
-        <v>0.4701</v>
+        <v>0.5839</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -2558,70 +2558,70 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1062.0106</v>
+        <v>1044.2531</v>
       </c>
       <c r="C4" t="n">
-        <v>228.0649</v>
+        <v>110.7656</v>
       </c>
       <c r="D4" t="n">
-        <v>68.2</v>
+        <v>67</v>
       </c>
       <c r="E4" t="n">
-        <v>14.9566</v>
+        <v>7.4833</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1374</v>
+        <v>0.1376</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.0012</v>
       </c>
       <c r="H4" t="n">
-        <v>2.43</v>
+        <v>2.454</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1068</v>
+        <v>0.1031</v>
       </c>
       <c r="J4" t="n">
-        <v>0.421</v>
+        <v>0.4375</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0461</v>
+        <v>0.0169</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4206</v>
+        <v>0.4359</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0462</v>
+        <v>0.0156</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1566</v>
+        <v>0.2125</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0689</v>
+        <v>0.0171</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0128</v>
+        <v>0.0127</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0005</v>
+        <v>0.0008</v>
       </c>
       <c r="R4" t="n">
-        <v>0.1501</v>
+        <v>0.149</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.0022</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1654</v>
+        <v>0.1661</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0045</v>
+        <v>0.0011</v>
       </c>
       <c r="V4" t="n">
-        <v>49.6088</v>
+        <v>49.8431</v>
       </c>
       <c r="W4" t="n">
-        <v>1.3431</v>
+        <v>0.3296</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -2661,70 +2661,70 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2320.8871</v>
+        <v>2115.6203</v>
       </c>
       <c r="C5" t="n">
-        <v>269.3897</v>
+        <v>1108.5954</v>
       </c>
       <c r="D5" t="n">
-        <v>67.8</v>
+        <v>61.6</v>
       </c>
       <c r="E5" t="n">
-        <v>8.012499999999999</v>
+        <v>32.807</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3339</v>
+        <v>0.3343</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0004</v>
+        <v>0.001</v>
       </c>
       <c r="H5" t="n">
-        <v>9.458</v>
+        <v>9.484</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0239</v>
+        <v>0.0378</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3777</v>
+        <v>0.3052</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0205</v>
+        <v>0.0955</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3778</v>
+        <v>0.3051</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0212</v>
+        <v>0.0959</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0762</v>
+        <v>0.0589</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0238</v>
+        <v>0.0114</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0221</v>
+        <v>0.0215</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0003</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="R5" t="n">
-        <v>0.1571</v>
+        <v>0.1562</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0017</v>
+        <v>0.0018</v>
       </c>
       <c r="T5" t="n">
-        <v>0.168</v>
+        <v>0.1696</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0014</v>
+        <v>0.0016</v>
       </c>
       <c r="V5" t="n">
-        <v>50.3969</v>
+        <v>50.8927</v>
       </c>
       <c r="W5" t="n">
-        <v>0.4226</v>
+        <v>0.4849</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -2764,70 +2764,70 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>664.6531</v>
+        <v>794.8181</v>
       </c>
       <c r="C6" t="n">
-        <v>133.4001</v>
+        <v>207.8824</v>
       </c>
       <c r="D6" t="n">
-        <v>28.8</v>
+        <v>34.8</v>
       </c>
       <c r="E6" t="n">
-        <v>6.0992</v>
+        <v>9.5237</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2049</v>
+        <v>0.2043</v>
       </c>
       <c r="G6" t="n">
         <v>0.0002</v>
       </c>
       <c r="H6" t="n">
-        <v>8.316000000000001</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.07920000000000001</v>
+        <v>0.1173</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8297</v>
+        <v>0.8326</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0073</v>
+        <v>0.0075</v>
       </c>
       <c r="L6" t="n">
-        <v>0.8274</v>
+        <v>0.8318</v>
       </c>
       <c r="M6" t="n">
         <v>0.0068</v>
       </c>
       <c r="N6" t="n">
-        <v>0.8192</v>
+        <v>0.8209</v>
       </c>
       <c r="O6" t="n">
-        <v>0.008200000000000001</v>
+        <v>0.0207</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0162</v>
+        <v>0.0164</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0004</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="R6" t="n">
         <v>0.1261</v>
       </c>
       <c r="S6" t="n">
-        <v>0.001</v>
+        <v>0.0001</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1103</v>
+        <v>0.1123</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0023</v>
+        <v>0.0019</v>
       </c>
       <c r="V6" t="n">
-        <v>33.0923</v>
+        <v>33.6761</v>
       </c>
       <c r="W6" t="n">
-        <v>0.6991000000000001</v>
+        <v>0.579</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -2867,70 +2867,70 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>681.3765</v>
+        <v>785.2026</v>
       </c>
       <c r="C7" t="n">
-        <v>96.3352</v>
+        <v>210.6798</v>
       </c>
       <c r="D7" t="n">
-        <v>45.4</v>
+        <v>53</v>
       </c>
       <c r="E7" t="n">
-        <v>6.6933</v>
+        <v>14.5945</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1293</v>
+        <v>0.1285</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0011</v>
+        <v>0.0008</v>
       </c>
       <c r="H7" t="n">
-        <v>6.048</v>
+        <v>6.054</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1966</v>
+        <v>0.1474</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8053</v>
+        <v>0.8102</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0048</v>
+        <v>0.0101</v>
       </c>
       <c r="L7" t="n">
-        <v>0.803</v>
+        <v>0.8078</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0055</v>
+        <v>0.0102</v>
       </c>
       <c r="N7" t="n">
-        <v>0.7992</v>
+        <v>0.8004</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0042</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0118</v>
+        <v>0.012</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0002</v>
+        <v>0.0004</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0954</v>
+        <v>0.09760000000000001</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0008</v>
+        <v>0.0016</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0868</v>
+        <v>0.0892</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0031</v>
+        <v>0.0015</v>
       </c>
       <c r="V7" t="n">
-        <v>26.0271</v>
+        <v>26.7598</v>
       </c>
       <c r="W7" t="n">
-        <v>0.9367</v>
+        <v>0.4603</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -2970,70 +2970,70 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>745.4105</v>
+        <v>652.972</v>
       </c>
       <c r="C8" t="n">
-        <v>121.3614</v>
+        <v>148.5232</v>
       </c>
       <c r="D8" t="n">
-        <v>55</v>
+        <v>48.4</v>
       </c>
       <c r="E8" t="n">
-        <v>9.055400000000001</v>
+        <v>11.6103</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1185</v>
+        <v>0.1173</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0018</v>
+        <v>0.0009</v>
       </c>
       <c r="H8" t="n">
-        <v>4.562</v>
+        <v>4.644</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0526</v>
+        <v>0.0844</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7783</v>
+        <v>0.7747000000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.0107</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7763</v>
+        <v>0.7725</v>
       </c>
       <c r="M8" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.0104</v>
       </c>
       <c r="N8" t="n">
-        <v>0.7734</v>
+        <v>0.7691</v>
       </c>
       <c r="O8" t="n">
-        <v>0.01</v>
+        <v>0.0122</v>
       </c>
       <c r="P8" t="n">
         <v>0.0105</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.0007</v>
+        <v>0.0004</v>
       </c>
       <c r="R8" t="n">
-        <v>0.0861</v>
+        <v>0.0852</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.001</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0873</v>
+        <v>0.0868</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0021</v>
+        <v>0.0022</v>
       </c>
       <c r="V8" t="n">
-        <v>26.1769</v>
+        <v>26.042</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6311</v>
+        <v>0.6642</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -3234,70 +3234,70 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>24.4761</v>
+        <v>65.6294</v>
       </c>
       <c r="C2" t="n">
-        <v>6.4351</v>
+        <v>13.0756</v>
       </c>
       <c r="D2" t="n">
-        <v>24.4</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>6.9498</v>
+        <v>15.1261</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0561</v>
+        <v>0.0568</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0005</v>
+        <v>0.0002</v>
       </c>
       <c r="H2" t="n">
-        <v>1.202</v>
+        <v>1.17</v>
       </c>
       <c r="I2" t="n">
-        <v>0.08840000000000001</v>
+        <v>0.0071</v>
       </c>
       <c r="J2" t="n">
-        <v>0.5357</v>
+        <v>0.5611</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0106</v>
+        <v>0.0068</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5357</v>
+        <v>0.5606</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0107</v>
+        <v>0.0068</v>
       </c>
       <c r="N2" t="n">
-        <v>0.5346</v>
+        <v>0.5606</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0106</v>
+        <v>0.0061</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0406</v>
+        <v>0.0413</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.001</v>
+        <v>0.0017</v>
       </c>
       <c r="R2" t="n">
-        <v>0.2932</v>
+        <v>0.2836</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0042</v>
+        <v>0.0019</v>
       </c>
       <c r="T2" t="n">
-        <v>0.3101</v>
+        <v>0.2991</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0074</v>
+        <v>0.0127</v>
       </c>
       <c r="V2" t="n">
-        <v>9.3024</v>
+        <v>8.9732</v>
       </c>
       <c r="W2" t="n">
-        <v>0.2216</v>
+        <v>0.3824</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -3337,70 +3337,70 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>74.7328</v>
+        <v>207.9008</v>
       </c>
       <c r="C3" t="n">
-        <v>31.104</v>
+        <v>33.0642</v>
       </c>
       <c r="D3" t="n">
-        <v>44.8</v>
+        <v>131</v>
       </c>
       <c r="E3" t="n">
-        <v>19.6774</v>
+        <v>21.3542</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1517</v>
+        <v>0.1504</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0009</v>
+        <v>0.0012</v>
       </c>
       <c r="H3" t="n">
-        <v>3.06</v>
+        <v>3.03</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>0.0274</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2986</v>
+        <v>0.449</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0982</v>
+        <v>0.013</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2982</v>
+        <v>0.4486</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0975</v>
+        <v>0.0128</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2923</v>
+        <v>0.443</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0956</v>
+        <v>0.0159</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0569</v>
+        <v>0.0578</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0042</v>
+        <v>0.0048</v>
       </c>
       <c r="R3" t="n">
-        <v>0.3122</v>
+        <v>0.313</v>
       </c>
       <c r="S3" t="n">
-        <v>0.009299999999999999</v>
+        <v>0.0115</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3927</v>
+        <v>0.3953</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0153</v>
+        <v>0.0208</v>
       </c>
       <c r="V3" t="n">
-        <v>11.7802</v>
+        <v>11.8581</v>
       </c>
       <c r="W3" t="n">
-        <v>0.4582</v>
+        <v>0.6237</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -3440,70 +3440,70 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>54.3158</v>
+        <v>204.2748</v>
       </c>
       <c r="C4" t="n">
-        <v>5.9872</v>
+        <v>45.0779</v>
       </c>
       <c r="D4" t="n">
-        <v>37.6</v>
+        <v>150.2</v>
       </c>
       <c r="E4" t="n">
-        <v>4.5607</v>
+        <v>34.1057</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1239</v>
+        <v>0.1234</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0019</v>
+        <v>0.0009</v>
       </c>
       <c r="H4" t="n">
-        <v>1.442</v>
+        <v>1.528</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0045</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2439</v>
+        <v>0.4226</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0194</v>
+        <v>0.0145</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2439</v>
+        <v>0.4221</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0194</v>
+        <v>0.0145</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1789</v>
+        <v>0.3096</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0464</v>
+        <v>0.0466</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0489</v>
+        <v>0.054</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0016</v>
+        <v>0.0053</v>
       </c>
       <c r="R4" t="n">
-        <v>0.4523</v>
+        <v>0.4481</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0078</v>
+        <v>0.0062</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5653</v>
+        <v>0.5735</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0199</v>
+        <v>0.0174</v>
       </c>
       <c r="V4" t="n">
-        <v>16.9577</v>
+        <v>17.2036</v>
       </c>
       <c r="W4" t="n">
-        <v>0.5984</v>
+        <v>0.5232</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -3543,70 +3543,70 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>136.0986</v>
+        <v>472.0184</v>
       </c>
       <c r="C5" t="n">
-        <v>42.4121</v>
+        <v>75.9178</v>
       </c>
       <c r="D5" t="n">
-        <v>44.8</v>
+        <v>162.2</v>
       </c>
       <c r="E5" t="n">
-        <v>14.5327</v>
+        <v>26.7432</v>
       </c>
       <c r="F5" t="n">
-        <v>0.332</v>
+        <v>0.3304</v>
       </c>
       <c r="G5" t="n">
+        <v>0.0027</v>
+      </c>
+      <c r="H5" t="n">
+        <v>8.978</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.0963</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.436</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.0381</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.4355</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.0382</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.1381</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.0822</v>
+      </c>
+      <c r="Q5" t="n">
         <v>0.0031</v>
       </c>
-      <c r="H5" t="n">
-        <v>8.917999999999999</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0.0179</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.2639</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0.0595</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0.2635</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0.0593</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0.1142</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0.0387</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0.09089999999999999</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0.0013</v>
-      </c>
       <c r="R5" t="n">
-        <v>0.4374</v>
+        <v>0.4408</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0113</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="T5" t="n">
-        <v>0.7069</v>
+        <v>0.7027</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0271</v>
+        <v>0.0073</v>
       </c>
       <c r="V5" t="n">
-        <v>21.2056</v>
+        <v>21.0808</v>
       </c>
       <c r="W5" t="n">
-        <v>0.8121</v>
+        <v>0.2181</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -3646,70 +3646,70 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>135.6359</v>
+        <v>389.3589</v>
       </c>
       <c r="C6" t="n">
-        <v>35.2028</v>
+        <v>56.7246</v>
       </c>
       <c r="D6" t="n">
-        <v>62.4</v>
+        <v>186.2</v>
       </c>
       <c r="E6" t="n">
-        <v>16.6373</v>
+        <v>28.6217</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1987</v>
+        <v>0.1992</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0003</v>
+        <v>0.0004</v>
       </c>
       <c r="H6" t="n">
-        <v>7.772</v>
+        <v>7.77</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0045</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3039</v>
+        <v>0.501</v>
       </c>
       <c r="K6" t="n">
-        <v>0.09329999999999999</v>
+        <v>0.0209</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3037</v>
+        <v>0.5004</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0931</v>
+        <v>0.0209</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2856</v>
+        <v>0.4851</v>
       </c>
       <c r="O6" t="n">
-        <v>0.099</v>
+        <v>0.0354</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0693</v>
+        <v>0.07240000000000001</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0053</v>
+        <v>0.0057</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3488</v>
+        <v>0.3406</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0078</v>
+        <v>0.0146</v>
       </c>
       <c r="T6" t="n">
-        <v>0.406</v>
+        <v>0.4032</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0141</v>
+        <v>0.0046</v>
       </c>
       <c r="V6" t="n">
-        <v>12.1801</v>
+        <v>12.0954</v>
       </c>
       <c r="W6" t="n">
-        <v>0.4224</v>
+        <v>0.1393</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -3749,70 +3749,70 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>64.33280000000001</v>
+        <v>278.9737</v>
       </c>
       <c r="C7" t="n">
-        <v>17.2109</v>
+        <v>2.0969</v>
       </c>
       <c r="D7" t="n">
-        <v>43.2</v>
+        <v>199</v>
       </c>
       <c r="E7" t="n">
-        <v>12.4579</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1194</v>
+        <v>0.1197</v>
       </c>
       <c r="G7" t="n">
         <v>0.0004</v>
       </c>
       <c r="H7" t="n">
-        <v>4.664</v>
+        <v>4.668</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0055</v>
+        <v>0.0045</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1567</v>
+        <v>0.4616</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0257</v>
+        <v>0.0058</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1567</v>
+        <v>0.461</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0258</v>
+        <v>0.0057</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1571</v>
+        <v>0.4593</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0254</v>
+        <v>0.0053</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0505</v>
+        <v>0.0485</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0051</v>
+        <v>0.0008</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2765</v>
+        <v>0.2846</v>
       </c>
       <c r="S7" t="n">
-        <v>0.01</v>
+        <v>0.0049</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3159</v>
+        <v>0.3157</v>
       </c>
       <c r="U7" t="n">
-        <v>0.012</v>
+        <v>0.007</v>
       </c>
       <c r="V7" t="n">
-        <v>9.478199999999999</v>
+        <v>9.471299999999999</v>
       </c>
       <c r="W7" t="n">
-        <v>0.3588</v>
+        <v>0.2108</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -3852,70 +3852,70 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>48.8456</v>
+        <v>243.739</v>
       </c>
       <c r="C8" t="n">
-        <v>26.0556</v>
+        <v>0.7625</v>
       </c>
       <c r="D8" t="n">
-        <v>37.6</v>
+        <v>199</v>
       </c>
       <c r="E8" t="n">
-        <v>21.2791</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1049</v>
+        <v>0.106</v>
       </c>
       <c r="G8" t="n">
+        <v>0.0005999999999999999</v>
+      </c>
+      <c r="H8" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.0224</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.3958</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.0228</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.3954</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.0229</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.3953</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.0229</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.0423</v>
+      </c>
+      <c r="Q8" t="n">
         <v>0.001</v>
       </c>
-      <c r="H8" t="n">
-        <v>3.51</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0.111</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0.0406</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0.111</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0.0407</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0.1109</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0.0406</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0.0452</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0.0045</v>
-      </c>
       <c r="R8" t="n">
-        <v>0.2785</v>
+        <v>0.2707</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0109</v>
+        <v>0.0072</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3306</v>
+        <v>0.317</v>
       </c>
       <c r="U8" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.0065</v>
       </c>
       <c r="V8" t="n">
-        <v>9.918200000000001</v>
+        <v>9.509399999999999</v>
       </c>
       <c r="W8" t="n">
-        <v>0.287</v>
+        <v>0.1936</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -4116,22 +4116,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>47.3548</v>
+        <v>95.8066</v>
       </c>
       <c r="C2" t="n">
-        <v>3.3678</v>
+        <v>12.7824</v>
       </c>
       <c r="D2" t="n">
-        <v>39.2</v>
+        <v>83</v>
       </c>
       <c r="E2" t="n">
-        <v>2.6833</v>
+        <v>11.4018</v>
       </c>
       <c r="F2" t="n">
-        <v>0.035</v>
+        <v>0.037</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0035</v>
+        <v>0.004</v>
       </c>
       <c r="H2" t="n">
         <v>0.68</v>
@@ -4140,46 +4140,46 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0.8331</v>
+        <v>0.8461</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0113</v>
+        <v>0.0058</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8338</v>
+        <v>0.8467</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0112</v>
+        <v>0.0054</v>
       </c>
       <c r="N2" t="n">
-        <v>0.8313</v>
+        <v>0.84</v>
       </c>
       <c r="O2" t="n">
-        <v>0.009299999999999999</v>
+        <v>0.0064</v>
       </c>
       <c r="P2" t="n">
-        <v>0.1406</v>
+        <v>0.1429</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0017</v>
+        <v>0.0023</v>
       </c>
       <c r="R2" t="n">
-        <v>0.697</v>
+        <v>0.7091</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0101</v>
+        <v>0.0204</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7272</v>
+        <v>0.7389</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0126</v>
+        <v>0.0238</v>
       </c>
       <c r="V2" t="n">
-        <v>8.726699999999999</v>
+        <v>8.8674</v>
       </c>
       <c r="W2" t="n">
-        <v>0.1517</v>
+        <v>0.2861</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -4219,22 +4219,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>64.2683</v>
+        <v>178.1379</v>
       </c>
       <c r="C3" t="n">
-        <v>3.916</v>
+        <v>34.8253</v>
       </c>
       <c r="D3" t="n">
-        <v>39.8</v>
+        <v>118</v>
       </c>
       <c r="E3" t="n">
-        <v>2.3875</v>
+        <v>24.0832</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1521</v>
+        <v>0.1524</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0023</v>
+        <v>0.0017</v>
       </c>
       <c r="H3" t="n">
         <v>2.32</v>
@@ -4243,46 +4243,46 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8316</v>
+        <v>0.861</v>
       </c>
       <c r="K3" t="n">
-        <v>0.016</v>
+        <v>0.013</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8324</v>
+        <v>0.8602</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0151</v>
+        <v>0.0127</v>
       </c>
       <c r="N3" t="n">
-        <v>0.8371</v>
+        <v>0.8597</v>
       </c>
       <c r="O3" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.0107</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1691</v>
+        <v>0.1716</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0122</v>
+        <v>0.0102</v>
       </c>
       <c r="R3" t="n">
-        <v>0.7759</v>
+        <v>0.7688</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0306</v>
+        <v>0.0321</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9292</v>
+        <v>0.9314</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0209</v>
+        <v>0.0253</v>
       </c>
       <c r="V3" t="n">
-        <v>11.1501</v>
+        <v>11.1772</v>
       </c>
       <c r="W3" t="n">
-        <v>0.2507</v>
+        <v>0.3042</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -4322,22 +4322,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>61.3298</v>
+        <v>134.312</v>
       </c>
       <c r="C4" t="n">
-        <v>6.2247</v>
+        <v>17.6529</v>
       </c>
       <c r="D4" t="n">
-        <v>41</v>
+        <v>95</v>
       </c>
       <c r="E4" t="n">
-        <v>4.4721</v>
+        <v>12.9422</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1255</v>
+        <v>0.1262</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.0007</v>
       </c>
       <c r="H4" t="n">
         <v>1.07</v>
@@ -4346,46 +4346,46 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8065</v>
+        <v>0.8387</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0205</v>
+        <v>0.0112</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8062</v>
+        <v>0.8388</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0205</v>
+        <v>0.0112</v>
       </c>
       <c r="N4" t="n">
-        <v>0.745</v>
+        <v>0.7514</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0563</v>
+        <v>0.0493</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1582</v>
+        <v>0.1591</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0109</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="R4" t="n">
-        <v>1.2438</v>
+        <v>1.2347</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0477</v>
+        <v>0.0128</v>
       </c>
       <c r="T4" t="n">
-        <v>1.4486</v>
+        <v>1.4847</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0383</v>
+        <v>0.0252</v>
       </c>
       <c r="V4" t="n">
-        <v>17.383</v>
+        <v>17.8165</v>
       </c>
       <c r="W4" t="n">
-        <v>0.4597</v>
+        <v>0.302</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -4425,19 +4425,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>92.7122</v>
+        <v>224.7787</v>
       </c>
       <c r="C5" t="n">
-        <v>10.8141</v>
+        <v>50.5633</v>
       </c>
       <c r="D5" t="n">
-        <v>43</v>
+        <v>110</v>
       </c>
       <c r="E5" t="n">
-        <v>5.4772</v>
+        <v>25.836</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3156</v>
+        <v>0.316</v>
       </c>
       <c r="G5" t="n">
         <v>0.0022</v>
@@ -4449,46 +4449,46 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8608</v>
+        <v>0.8753</v>
       </c>
       <c r="K5" t="n">
-        <v>0.013</v>
+        <v>0.0129</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8599</v>
+        <v>0.875</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0133</v>
+        <v>0.0122</v>
       </c>
       <c r="N5" t="n">
-        <v>0.6912</v>
+        <v>0.6812</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0277</v>
+        <v>0.0822</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2452</v>
+        <v>0.2437</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0041</v>
+        <v>0.0137</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9916</v>
+        <v>1.0027</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0191</v>
+        <v>0.0228</v>
       </c>
       <c r="T5" t="n">
-        <v>1.5693</v>
+        <v>1.5888</v>
       </c>
       <c r="U5" t="n">
-        <v>0.012</v>
+        <v>0.0187</v>
       </c>
       <c r="V5" t="n">
-        <v>18.8311</v>
+        <v>19.0653</v>
       </c>
       <c r="W5" t="n">
-        <v>0.144</v>
+        <v>0.2243</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -4528,22 +4528,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>84.7109</v>
+        <v>312.4196</v>
       </c>
       <c r="C6" t="n">
-        <v>24.5372</v>
+        <v>39.4625</v>
       </c>
       <c r="D6" t="n">
-        <v>46.4</v>
+        <v>182</v>
       </c>
       <c r="E6" t="n">
-        <v>13.5019</v>
+        <v>23.3452</v>
       </c>
       <c r="F6" t="n">
         <v>0.1829</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0003</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="H6" t="n">
         <v>7.13</v>
@@ -4552,46 +4552,46 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6923</v>
+        <v>0.8768</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0746</v>
+        <v>0.0156</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6912</v>
+        <v>0.877</v>
       </c>
       <c r="M6" t="n">
-        <v>0.07489999999999999</v>
+        <v>0.0159</v>
       </c>
       <c r="N6" t="n">
-        <v>0.5981</v>
+        <v>0.8614000000000001</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0983</v>
+        <v>0.0226</v>
       </c>
       <c r="P6" t="n">
-        <v>0.205</v>
+        <v>0.2044</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.0074</v>
       </c>
       <c r="R6" t="n">
-        <v>0.7593</v>
+        <v>0.7873</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0124</v>
+        <v>0.0175</v>
       </c>
       <c r="T6" t="n">
-        <v>0.9469</v>
+        <v>0.9617</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0145</v>
+        <v>0.048</v>
       </c>
       <c r="V6" t="n">
-        <v>11.3627</v>
+        <v>11.5406</v>
       </c>
       <c r="W6" t="n">
-        <v>0.1737</v>
+        <v>0.5764</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -4631,19 +4631,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>58.9315</v>
+        <v>277.6454</v>
       </c>
       <c r="C7" t="n">
-        <v>1.7498</v>
+        <v>1.0524</v>
       </c>
       <c r="D7" t="n">
-        <v>38.8</v>
+        <v>199</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4472</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1114</v>
+        <v>0.1119</v>
       </c>
       <c r="G7" t="n">
         <v>0.0005</v>
@@ -4655,46 +4655,46 @@
         <v>0.0055</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7195</v>
+        <v>0.878</v>
       </c>
       <c r="K7" t="n">
-        <v>0.027</v>
+        <v>0.0067</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7181999999999999</v>
+        <v>0.8782</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0272</v>
+        <v>0.0067</v>
       </c>
       <c r="N7" t="n">
-        <v>0.7062</v>
+        <v>0.8763</v>
       </c>
       <c r="O7" t="n">
-        <v>0.029</v>
+        <v>0.0083</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1779</v>
+        <v>0.1495</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0062</v>
+        <v>0.0043</v>
       </c>
       <c r="R7" t="n">
-        <v>0.6599</v>
+        <v>0.6919</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0115</v>
+        <v>0.0282</v>
       </c>
       <c r="T7" t="n">
-        <v>0.7392</v>
+        <v>0.7472</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0145</v>
+        <v>0.0136</v>
       </c>
       <c r="V7" t="n">
-        <v>8.8706</v>
+        <v>8.966100000000001</v>
       </c>
       <c r="W7" t="n">
-        <v>0.1743</v>
+        <v>0.163</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -4734,70 +4734,70 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>55.3798</v>
+        <v>262.8867</v>
       </c>
       <c r="C8" t="n">
-        <v>1.123</v>
+        <v>3.5415</v>
       </c>
       <c r="D8" t="n">
-        <v>38.8</v>
+        <v>199</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4472</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1015</v>
+        <v>0.1031</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001</v>
+        <v>0.0008</v>
       </c>
       <c r="H8" t="n">
-        <v>2.81</v>
+        <v>2.814</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>0.0089</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7058</v>
+        <v>0.8696</v>
       </c>
       <c r="K8" t="n">
-        <v>0.021</v>
+        <v>0.0073</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7054</v>
+        <v>0.8702</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0214</v>
+        <v>0.0073</v>
       </c>
       <c r="N8" t="n">
-        <v>0.6916</v>
+        <v>0.8696</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0355</v>
+        <v>0.0068</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1468</v>
+        <v>0.1392</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.0105</v>
+        <v>0.0034</v>
       </c>
       <c r="R8" t="n">
-        <v>0.7004</v>
+        <v>0.6622</v>
       </c>
       <c r="S8" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.0067</v>
       </c>
       <c r="T8" t="n">
-        <v>0.8046</v>
+        <v>0.7863</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0217</v>
+        <v>0.0148</v>
       </c>
       <c r="V8" t="n">
-        <v>9.655099999999999</v>
+        <v>9.4353</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2603</v>
+        <v>0.1777</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -4998,70 +4998,70 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>34.5481</v>
+        <v>42.9973</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9897</v>
+        <v>3.1193</v>
       </c>
       <c r="D2" t="n">
-        <v>106</v>
+        <v>138</v>
       </c>
       <c r="E2" t="n">
-        <v>4.4721</v>
+        <v>10.8397</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0295</v>
+        <v>0.0297</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0003</v>
+        <v>0.0004</v>
       </c>
       <c r="H2" t="n">
-        <v>0.768</v>
+        <v>0.8</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0622</v>
+        <v>0.0308</v>
       </c>
       <c r="J2" t="n">
-        <v>0.6473</v>
+        <v>0.6543</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0132</v>
+        <v>0.0151</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6477000000000001</v>
+        <v>0.6543</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0141</v>
+        <v>0.0144</v>
       </c>
       <c r="N2" t="n">
-        <v>0.6363</v>
+        <v>0.6474</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0194</v>
+        <v>0.0168</v>
       </c>
       <c r="P2" t="n">
-        <v>0.1662</v>
+        <v>0.1691</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0028</v>
+        <v>0.0045</v>
       </c>
       <c r="R2" t="n">
-        <v>0.4033</v>
+        <v>0.4008</v>
       </c>
       <c r="S2" t="n">
-        <v>0.005</v>
+        <v>0.0041</v>
       </c>
       <c r="T2" t="n">
-        <v>0.509</v>
+        <v>0.5096000000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0021</v>
+        <v>0.0055</v>
       </c>
       <c r="V2" t="n">
-        <v>3.0537</v>
+        <v>3.0574</v>
       </c>
       <c r="W2" t="n">
-        <v>0.0127</v>
+        <v>0.033</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -5101,70 +5101,70 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>51.6329</v>
+        <v>63.6435</v>
       </c>
       <c r="C3" t="n">
-        <v>2.3252</v>
+        <v>6.3142</v>
       </c>
       <c r="D3" t="n">
-        <v>109</v>
+        <v>139</v>
       </c>
       <c r="E3" t="n">
-        <v>6.1237</v>
+        <v>15.8114</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1573</v>
+        <v>0.157</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0015</v>
+        <v>0.0016</v>
       </c>
       <c r="H3" t="n">
-        <v>1.864</v>
+        <v>1.872</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0537</v>
+        <v>0.0179</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7454</v>
+        <v>0.7521</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0256</v>
+        <v>0.0139</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7486</v>
+        <v>0.7562</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0257</v>
+        <v>0.0111</v>
       </c>
       <c r="N3" t="n">
-        <v>0.7379</v>
+        <v>0.7456</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0216</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2221</v>
+        <v>0.227</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0221</v>
+        <v>0.0246</v>
       </c>
       <c r="R3" t="n">
-        <v>0.504</v>
+        <v>0.509</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0252</v>
+        <v>0.0294</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8585</v>
+        <v>0.8697</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0332</v>
+        <v>0.0365</v>
       </c>
       <c r="V3" t="n">
-        <v>5.1512</v>
+        <v>5.218</v>
       </c>
       <c r="W3" t="n">
-        <v>0.1992</v>
+        <v>0.2193</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -5204,70 +5204,70 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>46.0636</v>
+        <v>63.0023</v>
       </c>
       <c r="C4" t="n">
-        <v>2.4588</v>
+        <v>4.6552</v>
       </c>
       <c r="D4" t="n">
-        <v>111</v>
+        <v>155</v>
       </c>
       <c r="E4" t="n">
-        <v>5.7009</v>
+        <v>11.9373</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1303</v>
+        <v>0.1301</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0022</v>
+        <v>0.0017</v>
       </c>
       <c r="H4" t="n">
-        <v>0.862</v>
+        <v>0.896</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0179</v>
+        <v>0.0195</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.7078</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0439</v>
+        <v>0.0241</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6859</v>
+        <v>0.7115</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0447</v>
+        <v>0.0258</v>
       </c>
       <c r="N4" t="n">
-        <v>0.6525</v>
+        <v>0.6208</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0489</v>
+        <v>0.0357</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2226</v>
+        <v>0.1935</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0273</v>
+        <v>0.0233</v>
       </c>
       <c r="R4" t="n">
-        <v>0.492</v>
+        <v>0.5131</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0036</v>
+        <v>0.0275</v>
       </c>
       <c r="T4" t="n">
-        <v>1.105</v>
+        <v>1.1232</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0359</v>
+        <v>0.0362</v>
       </c>
       <c r="V4" t="n">
-        <v>6.6298</v>
+        <v>6.739</v>
       </c>
       <c r="W4" t="n">
-        <v>0.2153</v>
+        <v>0.2169</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -5307,70 +5307,70 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>75.09399999999999</v>
+        <v>107.8128</v>
       </c>
       <c r="C5" t="n">
-        <v>2.8956</v>
+        <v>21.9706</v>
       </c>
       <c r="D5" t="n">
-        <v>110</v>
+        <v>162</v>
       </c>
       <c r="E5" t="n">
-        <v>4.1833</v>
+        <v>34.2053</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2952</v>
+        <v>0.2965</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0014</v>
+        <v>0.002</v>
       </c>
       <c r="H5" t="n">
-        <v>6.448</v>
+        <v>6.456</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0179</v>
+        <v>0.0219</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7035</v>
+        <v>0.6977</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0429</v>
+        <v>0.0365</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7052</v>
+        <v>0.6982</v>
       </c>
       <c r="M5" t="n">
-        <v>0.043</v>
+        <v>0.0386</v>
       </c>
       <c r="N5" t="n">
-        <v>0.5599</v>
+        <v>0.5525</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1397</v>
+        <v>0.1179</v>
       </c>
       <c r="P5" t="n">
-        <v>0.3623</v>
+        <v>0.3561</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0034</v>
+        <v>0.0263</v>
       </c>
       <c r="R5" t="n">
-        <v>0.916</v>
+        <v>0.8987000000000001</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0419</v>
+        <v>0.0223</v>
       </c>
       <c r="T5" t="n">
-        <v>2.211</v>
+        <v>2.2064</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0273</v>
+        <v>0.0259</v>
       </c>
       <c r="V5" t="n">
-        <v>13.2662</v>
+        <v>13.2386</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1639</v>
+        <v>0.1554</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -5410,70 +5410,70 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>64.6746</v>
+        <v>77.9144</v>
       </c>
       <c r="C6" t="n">
-        <v>2.5369</v>
+        <v>4.9424</v>
       </c>
       <c r="D6" t="n">
-        <v>106</v>
+        <v>133</v>
       </c>
       <c r="E6" t="n">
-        <v>4.4721</v>
+        <v>8.9443</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1636</v>
+        <v>0.1643</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0003</v>
+        <v>0.0014</v>
       </c>
       <c r="H6" t="n">
-        <v>5.736</v>
+        <v>5.79</v>
       </c>
       <c r="I6" t="n">
-        <v>0.065</v>
+        <v>0.0424</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6042</v>
+        <v>0.6045</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0027</v>
+        <v>0.0051</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6048</v>
+        <v>0.6046</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0018</v>
+        <v>0.0045</v>
       </c>
       <c r="N6" t="n">
-        <v>0.5894</v>
+        <v>0.5896</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0095</v>
+        <v>0.0141</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2765</v>
+        <v>0.2783</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0058</v>
+        <v>0.0205</v>
       </c>
       <c r="R6" t="n">
-        <v>0.5245</v>
+        <v>0.5132</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0245</v>
+        <v>0.006</v>
       </c>
       <c r="T6" t="n">
-        <v>1.0278</v>
+        <v>1.0028</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0354</v>
+        <v>0.0273</v>
       </c>
       <c r="V6" t="n">
-        <v>6.1668</v>
+        <v>6.0171</v>
       </c>
       <c r="W6" t="n">
-        <v>0.2123</v>
+        <v>0.1637</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -5513,70 +5513,70 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>48.6507</v>
+        <v>56.2247</v>
       </c>
       <c r="C7" t="n">
-        <v>3.4735</v>
+        <v>5.0812</v>
       </c>
       <c r="D7" t="n">
-        <v>109</v>
+        <v>131</v>
       </c>
       <c r="E7" t="n">
-        <v>8.660299999999999</v>
+        <v>13.0384</v>
       </c>
       <c r="F7" t="n">
-        <v>0.104</v>
+        <v>0.1044</v>
       </c>
       <c r="G7" t="n">
-        <v>0.001</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>3.412</v>
+        <v>3.48</v>
       </c>
       <c r="I7" t="n">
-        <v>0.07530000000000001</v>
+        <v>0.1562</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6052</v>
+        <v>0.613</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0074</v>
+        <v>0.0046</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6046</v>
+        <v>0.6131</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0071</v>
+        <v>0.0044</v>
       </c>
       <c r="N7" t="n">
-        <v>0.5503</v>
+        <v>0.577</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1222</v>
+        <v>0.0379</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1826</v>
+        <v>0.187</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0056</v>
+        <v>0.0064</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3664</v>
+        <v>0.3535</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0354</v>
+        <v>0.0214</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5762</v>
+        <v>0.5827</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0047</v>
+        <v>0.0081</v>
       </c>
       <c r="V7" t="n">
-        <v>3.4575</v>
+        <v>3.496</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0279</v>
+        <v>0.0489</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -5616,70 +5616,70 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>44.7079</v>
+        <v>51.4643</v>
       </c>
       <c r="C8" t="n">
-        <v>2.7248</v>
+        <v>3.3934</v>
       </c>
       <c r="D8" t="n">
-        <v>117</v>
+        <v>136</v>
       </c>
       <c r="E8" t="n">
-        <v>8.3666</v>
+        <v>10.9545</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1048</v>
+        <v>0.1055</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0007</v>
+        <v>0.0016</v>
       </c>
       <c r="H8" t="n">
-        <v>2.256</v>
+        <v>2.416</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1048</v>
+        <v>0.4454</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6125</v>
+        <v>0.6074000000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0053</v>
+        <v>0.0046</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6127</v>
+        <v>0.608</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0069</v>
+        <v>0.0047</v>
       </c>
       <c r="N8" t="n">
-        <v>0.6104000000000001</v>
+        <v>0.6092</v>
       </c>
       <c r="O8" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.0059</v>
       </c>
       <c r="P8" t="n">
-        <v>0.164</v>
+        <v>0.1649</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.0037</v>
+        <v>0.0027</v>
       </c>
       <c r="R8" t="n">
-        <v>0.349</v>
+        <v>0.3365</v>
       </c>
       <c r="S8" t="n">
+        <v>0.0042</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.6385999999999999</v>
+      </c>
+      <c r="U8" t="n">
         <v>0.0236</v>
       </c>
-      <c r="T8" t="n">
-        <v>0.6497000000000001</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0.0339</v>
-      </c>
       <c r="V8" t="n">
-        <v>3.8979</v>
+        <v>3.8314</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2032</v>
+        <v>0.1419</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -5880,70 +5880,70 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>37.1667</v>
+        <v>48.1218</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5542</v>
+        <v>4.8378</v>
       </c>
       <c r="D2" t="n">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="E2" t="n">
-        <v>2.7386</v>
+        <v>16.0468</v>
       </c>
       <c r="F2" t="n">
         <v>0.0307</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0002</v>
+        <v>0.0004</v>
       </c>
       <c r="H2" t="n">
-        <v>0.786</v>
+        <v>0.762</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0219</v>
+        <v>0.0963</v>
       </c>
       <c r="J2" t="n">
-        <v>0.6477000000000001</v>
+        <v>0.6605</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0112</v>
+        <v>0.0125</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5951</v>
+        <v>0.6091</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0139</v>
+        <v>0.0152</v>
       </c>
       <c r="N2" t="n">
-        <v>0.6092</v>
+        <v>0.6198</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0135</v>
+        <v>0.0133</v>
       </c>
       <c r="P2" t="n">
-        <v>0.1935</v>
+        <v>0.1946</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0055</v>
+        <v>0.0038</v>
       </c>
       <c r="R2" t="n">
-        <v>0.5492</v>
+        <v>0.5562</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0146</v>
+        <v>0.0041</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6689000000000001</v>
+        <v>0.6625</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0108</v>
+        <v>0.0136</v>
       </c>
       <c r="V2" t="n">
-        <v>4.0133</v>
+        <v>3.9748</v>
       </c>
       <c r="W2" t="n">
-        <v>0.06510000000000001</v>
+        <v>0.0818</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -5983,70 +5983,70 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>54.8965</v>
+        <v>69.98739999999999</v>
       </c>
       <c r="C3" t="n">
-        <v>2.7968</v>
+        <v>8.258599999999999</v>
       </c>
       <c r="D3" t="n">
-        <v>110</v>
+        <v>143</v>
       </c>
       <c r="E3" t="n">
-        <v>5.4772</v>
+        <v>17.4642</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1585</v>
+        <v>0.1582</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0029</v>
+        <v>0.0014</v>
       </c>
       <c r="H3" t="n">
-        <v>1.876</v>
+        <v>1.838</v>
       </c>
       <c r="I3" t="n">
-        <v>0.07770000000000001</v>
+        <v>0.0383</v>
       </c>
       <c r="J3" t="n">
-        <v>0.643</v>
+        <v>0.6705</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0234</v>
+        <v>0.0178</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5833</v>
+        <v>0.616</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0188</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5893</v>
+        <v>0.5999</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0222</v>
+        <v>0.0246</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2554</v>
+        <v>0.2511</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0268</v>
+        <v>0.0278</v>
       </c>
       <c r="R3" t="n">
-        <v>0.6636</v>
+        <v>0.6652</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0271</v>
+        <v>0.0319</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9852</v>
+        <v>1.0249</v>
       </c>
       <c r="U3" t="n">
-        <v>0.008200000000000001</v>
+        <v>0.0351</v>
       </c>
       <c r="V3" t="n">
-        <v>5.9114</v>
+        <v>6.1495</v>
       </c>
       <c r="W3" t="n">
-        <v>0.049</v>
+        <v>0.2109</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -6086,70 +6086,70 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>49.7985</v>
+        <v>72.14490000000001</v>
       </c>
       <c r="C4" t="n">
-        <v>1.3219</v>
+        <v>11.0091</v>
       </c>
       <c r="D4" t="n">
-        <v>113</v>
+        <v>168</v>
       </c>
       <c r="E4" t="n">
-        <v>4.1833</v>
+        <v>27.2489</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1315</v>
+        <v>0.1297</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0011</v>
+        <v>0.001</v>
       </c>
       <c r="H4" t="n">
-        <v>0.874</v>
+        <v>0.886</v>
       </c>
       <c r="I4" t="n">
-        <v>0.055</v>
+        <v>0.0434</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.6067</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0541</v>
+        <v>0.0409</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4865</v>
+        <v>0.539</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0585</v>
+        <v>0.0587</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3961</v>
+        <v>0.4197</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0187</v>
+        <v>0.0291</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2203</v>
+        <v>0.202</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0284</v>
+        <v>0.0027</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8308</v>
+        <v>0.8106</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0307</v>
+        <v>0.0257</v>
       </c>
       <c r="T4" t="n">
-        <v>1.3844</v>
+        <v>1.3579</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0118</v>
+        <v>0.0131</v>
       </c>
       <c r="V4" t="n">
-        <v>8.3066</v>
+        <v>8.147500000000001</v>
       </c>
       <c r="W4" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.07870000000000001</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -6189,70 +6189,70 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>77.0663</v>
+        <v>118.1362</v>
       </c>
       <c r="C5" t="n">
-        <v>4.087</v>
+        <v>16.3217</v>
       </c>
       <c r="D5" t="n">
-        <v>110</v>
+        <v>170</v>
       </c>
       <c r="E5" t="n">
-        <v>4.1833</v>
+        <v>24.3413</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2974</v>
+        <v>0.2983</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0018</v>
+        <v>0.0015</v>
       </c>
       <c r="H5" t="n">
-        <v>6.456</v>
+        <v>6.488</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0219</v>
+        <v>0.0179</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6011</v>
+        <v>0.6368</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0147</v>
+        <v>0.0192</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5246</v>
+        <v>0.5558</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0244</v>
+        <v>0.0449</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3257</v>
+        <v>0.3435</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0121</v>
+        <v>0.0253</v>
       </c>
       <c r="P5" t="n">
-        <v>0.3543</v>
+        <v>0.3917</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.031</v>
+        <v>0.0059</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1077</v>
+        <v>1.0683</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0152</v>
+        <v>0.0248</v>
       </c>
       <c r="T5" t="n">
-        <v>2.3701</v>
+        <v>2.3457</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0325</v>
+        <v>0.0373</v>
       </c>
       <c r="V5" t="n">
-        <v>14.2206</v>
+        <v>14.0742</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1951</v>
+        <v>0.2238</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -6292,70 +6292,70 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>86.33320000000001</v>
+        <v>135.7699</v>
       </c>
       <c r="C6" t="n">
-        <v>14.1691</v>
+        <v>2.0528</v>
       </c>
       <c r="D6" t="n">
-        <v>124</v>
+        <v>199</v>
       </c>
       <c r="E6" t="n">
-        <v>19.3649</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
         <v>0.1655</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0011</v>
+        <v>0.0008</v>
       </c>
       <c r="H6" t="n">
-        <v>5.732</v>
+        <v>5.778</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0045</v>
+        <v>0.06909999999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4962</v>
+        <v>0.63</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0658</v>
+        <v>0.037</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4749</v>
+        <v>0.6048</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0575</v>
+        <v>0.034</v>
       </c>
       <c r="N6" t="n">
-        <v>0.4443</v>
+        <v>0.5725</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0546</v>
+        <v>0.0171</v>
       </c>
       <c r="P6" t="n">
-        <v>0.3142</v>
+        <v>0.2972</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0266</v>
+        <v>0.0058</v>
       </c>
       <c r="R6" t="n">
-        <v>0.6629</v>
+        <v>0.6653</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0111</v>
+        <v>0.0055</v>
       </c>
       <c r="T6" t="n">
-        <v>1.1522</v>
+        <v>1.1411</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0269</v>
+        <v>0.0092</v>
       </c>
       <c r="V6" t="n">
-        <v>6.9134</v>
+        <v>6.8468</v>
       </c>
       <c r="W6" t="n">
-        <v>0.1616</v>
+        <v>0.0549</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -6395,70 +6395,70 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>61.8054</v>
+        <v>96.6665</v>
       </c>
       <c r="C7" t="n">
-        <v>8.3467</v>
+        <v>1.3598</v>
       </c>
       <c r="D7" t="n">
-        <v>125</v>
+        <v>199</v>
       </c>
       <c r="E7" t="n">
-        <v>17.1026</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1049</v>
+        <v>0.1046</v>
       </c>
       <c r="G7" t="n">
-        <v>0.001</v>
+        <v>0.0005</v>
       </c>
       <c r="H7" t="n">
         <v>3.398</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0955</v>
+        <v>0.0517</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4998</v>
+        <v>0.5972</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0598</v>
+        <v>0.0196</v>
       </c>
       <c r="L7" t="n">
-        <v>0.4795</v>
+        <v>0.5631</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0498</v>
+        <v>0.0195</v>
       </c>
       <c r="N7" t="n">
-        <v>0.4555</v>
+        <v>0.555</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0444</v>
+        <v>0.0156</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2062</v>
+        <v>0.2112</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0041</v>
+        <v>0.0033</v>
       </c>
       <c r="R7" t="n">
-        <v>0.4984</v>
+        <v>0.4985</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0275</v>
+        <v>0.0056</v>
       </c>
       <c r="T7" t="n">
-        <v>0.731</v>
+        <v>0.7391</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0056</v>
+        <v>0.0111</v>
       </c>
       <c r="V7" t="n">
-        <v>4.3858</v>
+        <v>4.4344</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0337</v>
+        <v>0.0664</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -6498,70 +6498,70 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>50.2461</v>
+        <v>79.1786</v>
       </c>
       <c r="C8" t="n">
-        <v>11.987</v>
+        <v>2.2669</v>
       </c>
       <c r="D8" t="n">
-        <v>122</v>
+        <v>197</v>
       </c>
       <c r="E8" t="n">
-        <v>29.2831</v>
+        <v>4.4721</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1046</v>
+        <v>0.105</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.0011</v>
       </c>
       <c r="H8" t="n">
-        <v>2.242</v>
+        <v>2.342</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0438</v>
+        <v>0.1564</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4517</v>
+        <v>0.5599</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1063</v>
+        <v>0.0181</v>
       </c>
       <c r="L8" t="n">
-        <v>0.4076</v>
+        <v>0.5037</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0987</v>
+        <v>0.0206</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3974</v>
+        <v>0.4792</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0771</v>
+        <v>0.0364</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1812</v>
+        <v>0.1835</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.003</v>
+        <v>0.0062</v>
       </c>
       <c r="R8" t="n">
-        <v>0.5088</v>
+        <v>0.5067</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0101</v>
+        <v>0.0229</v>
       </c>
       <c r="T8" t="n">
-        <v>0.7991</v>
+        <v>0.8072</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0381</v>
+        <v>0.0254</v>
       </c>
       <c r="V8" t="n">
-        <v>4.7943</v>
+        <v>4.8431</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2288</v>
+        <v>0.1525</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
